--- a/output/version3/test/20-10/MARL/CTDE/RL-RL with EP (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-10/MARL/CTDE/RL-RL with EP (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C2" t="n">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="D2" t="n">
-        <v>911</v>
+        <v>817</v>
       </c>
       <c r="E2" t="n">
-        <v>951</v>
+        <v>868</v>
       </c>
       <c r="F2" t="n">
-        <v>849</v>
+        <v>924</v>
       </c>
       <c r="G2" t="n">
-        <v>842</v>
+        <v>860</v>
       </c>
       <c r="H2" t="n">
-        <v>864</v>
+        <v>837</v>
       </c>
       <c r="I2" t="n">
-        <v>938</v>
+        <v>965</v>
       </c>
       <c r="J2" t="n">
-        <v>928</v>
+        <v>884</v>
       </c>
       <c r="K2" t="n">
-        <v>904</v>
+        <v>807</v>
       </c>
       <c r="L2" t="n">
-        <v>894.3</v>
+        <v>870.6</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>908</v>
+        <v>893</v>
       </c>
       <c r="C3" t="n">
-        <v>744</v>
+        <v>931</v>
       </c>
       <c r="D3" t="n">
-        <v>1042</v>
+        <v>872</v>
       </c>
       <c r="E3" t="n">
-        <v>865</v>
+        <v>971</v>
       </c>
       <c r="F3" t="n">
-        <v>899</v>
+        <v>1029</v>
       </c>
       <c r="G3" t="n">
-        <v>853</v>
+        <v>931</v>
       </c>
       <c r="H3" t="n">
-        <v>892</v>
+        <v>988</v>
       </c>
       <c r="I3" t="n">
-        <v>816</v>
+        <v>893</v>
       </c>
       <c r="J3" t="n">
-        <v>858</v>
+        <v>889</v>
       </c>
       <c r="K3" t="n">
-        <v>935</v>
+        <v>862</v>
       </c>
       <c r="L3" t="n">
-        <v>881.2</v>
+        <v>925.9</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>952</v>
+        <v>888</v>
       </c>
       <c r="C4" t="n">
-        <v>848</v>
+        <v>941</v>
       </c>
       <c r="D4" t="n">
-        <v>858</v>
+        <v>874</v>
       </c>
       <c r="E4" t="n">
-        <v>933</v>
+        <v>845</v>
       </c>
       <c r="F4" t="n">
-        <v>782</v>
+        <v>899</v>
       </c>
       <c r="G4" t="n">
-        <v>844</v>
+        <v>920</v>
       </c>
       <c r="H4" t="n">
-        <v>922</v>
+        <v>910</v>
       </c>
       <c r="I4" t="n">
-        <v>997</v>
+        <v>942</v>
       </c>
       <c r="J4" t="n">
-        <v>788</v>
+        <v>867</v>
       </c>
       <c r="K4" t="n">
-        <v>798</v>
+        <v>886</v>
       </c>
       <c r="L4" t="n">
-        <v>872.2</v>
+        <v>897.2</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>909</v>
+        <v>789</v>
       </c>
       <c r="C5" t="n">
-        <v>890</v>
+        <v>818</v>
       </c>
       <c r="D5" t="n">
-        <v>960</v>
+        <v>832</v>
       </c>
       <c r="E5" t="n">
+        <v>809</v>
+      </c>
+      <c r="F5" t="n">
+        <v>838</v>
+      </c>
+      <c r="G5" t="n">
+        <v>830</v>
+      </c>
+      <c r="H5" t="n">
+        <v>806</v>
+      </c>
+      <c r="I5" t="n">
+        <v>777</v>
+      </c>
+      <c r="J5" t="n">
         <v>847</v>
       </c>
-      <c r="F5" t="n">
-        <v>833</v>
-      </c>
-      <c r="G5" t="n">
-        <v>844</v>
-      </c>
-      <c r="H5" t="n">
-        <v>841</v>
-      </c>
-      <c r="I5" t="n">
-        <v>837</v>
-      </c>
-      <c r="J5" t="n">
-        <v>823</v>
-      </c>
       <c r="K5" t="n">
-        <v>849</v>
+        <v>883</v>
       </c>
       <c r="L5" t="n">
-        <v>863.3</v>
+        <v>822.9</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>939</v>
+        <v>1028</v>
       </c>
       <c r="C6" t="n">
-        <v>1037</v>
+        <v>929</v>
       </c>
       <c r="D6" t="n">
-        <v>896</v>
+        <v>883</v>
       </c>
       <c r="E6" t="n">
-        <v>801</v>
+        <v>858</v>
       </c>
       <c r="F6" t="n">
-        <v>860</v>
+        <v>975</v>
       </c>
       <c r="G6" t="n">
-        <v>805</v>
+        <v>888</v>
       </c>
       <c r="H6" t="n">
-        <v>924</v>
+        <v>887</v>
       </c>
       <c r="I6" t="n">
-        <v>872</v>
+        <v>799</v>
       </c>
       <c r="J6" t="n">
-        <v>994</v>
+        <v>1052</v>
       </c>
       <c r="K6" t="n">
-        <v>804</v>
+        <v>861</v>
       </c>
       <c r="L6" t="n">
-        <v>893.2</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="C7" t="n">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="D7" t="n">
-        <v>953</v>
+        <v>927</v>
       </c>
       <c r="E7" t="n">
-        <v>896</v>
+        <v>848</v>
       </c>
       <c r="F7" t="n">
-        <v>912</v>
+        <v>820</v>
       </c>
       <c r="G7" t="n">
-        <v>898</v>
+        <v>860</v>
       </c>
       <c r="H7" t="n">
-        <v>801</v>
+        <v>835</v>
       </c>
       <c r="I7" t="n">
-        <v>925</v>
+        <v>861</v>
       </c>
       <c r="J7" t="n">
-        <v>827</v>
+        <v>941</v>
       </c>
       <c r="K7" t="n">
-        <v>1004</v>
+        <v>855</v>
       </c>
       <c r="L7" t="n">
-        <v>895.2</v>
+        <v>869.4</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>922</v>
+        <v>883</v>
       </c>
       <c r="C8" t="n">
-        <v>860</v>
+        <v>1057</v>
       </c>
       <c r="D8" t="n">
-        <v>915</v>
+        <v>1021</v>
       </c>
       <c r="E8" t="n">
-        <v>1006</v>
+        <v>940</v>
       </c>
       <c r="F8" t="n">
-        <v>891</v>
+        <v>1057</v>
       </c>
       <c r="G8" t="n">
-        <v>897</v>
+        <v>952</v>
       </c>
       <c r="H8" t="n">
-        <v>938</v>
+        <v>912</v>
       </c>
       <c r="I8" t="n">
-        <v>1035</v>
+        <v>901</v>
       </c>
       <c r="J8" t="n">
-        <v>1009</v>
+        <v>1020</v>
       </c>
       <c r="K8" t="n">
-        <v>955</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>942.8</v>
+        <v>974.3</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>924</v>
+        <v>1005</v>
       </c>
       <c r="C9" t="n">
-        <v>911</v>
+        <v>939</v>
       </c>
       <c r="D9" t="n">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="E9" t="n">
-        <v>938</v>
+        <v>1051</v>
       </c>
       <c r="F9" t="n">
-        <v>893</v>
+        <v>953</v>
       </c>
       <c r="G9" t="n">
-        <v>936</v>
+        <v>882</v>
       </c>
       <c r="H9" t="n">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="I9" t="n">
-        <v>867</v>
+        <v>950</v>
       </c>
       <c r="J9" t="n">
-        <v>986</v>
+        <v>914</v>
       </c>
       <c r="K9" t="n">
-        <v>880</v>
+        <v>948</v>
       </c>
       <c r="L9" t="n">
-        <v>914.3</v>
+        <v>945.7</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>817</v>
+        <v>861</v>
       </c>
       <c r="C10" t="n">
-        <v>921</v>
+        <v>910</v>
       </c>
       <c r="D10" t="n">
-        <v>824</v>
+        <v>762</v>
       </c>
       <c r="E10" t="n">
-        <v>727</v>
+        <v>896</v>
       </c>
       <c r="F10" t="n">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="G10" t="n">
-        <v>791</v>
+        <v>907</v>
       </c>
       <c r="H10" t="n">
-        <v>818</v>
+        <v>863</v>
       </c>
       <c r="I10" t="n">
-        <v>803</v>
+        <v>874</v>
       </c>
       <c r="J10" t="n">
-        <v>820</v>
+        <v>850</v>
       </c>
       <c r="K10" t="n">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="L10" t="n">
-        <v>822.6</v>
+        <v>865.9</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
+        <v>956</v>
+      </c>
+      <c r="C11" t="n">
+        <v>903</v>
+      </c>
+      <c r="D11" t="n">
+        <v>976</v>
+      </c>
+      <c r="E11" t="n">
+        <v>883</v>
+      </c>
+      <c r="F11" t="n">
+        <v>977</v>
+      </c>
+      <c r="G11" t="n">
+        <v>910</v>
+      </c>
+      <c r="H11" t="n">
+        <v>943</v>
+      </c>
+      <c r="I11" t="n">
+        <v>991</v>
+      </c>
+      <c r="J11" t="n">
+        <v>857</v>
+      </c>
+      <c r="K11" t="n">
         <v>854</v>
       </c>
-      <c r="C11" t="n">
-        <v>849</v>
-      </c>
-      <c r="D11" t="n">
-        <v>807</v>
-      </c>
-      <c r="E11" t="n">
-        <v>816</v>
-      </c>
-      <c r="F11" t="n">
-        <v>822</v>
-      </c>
-      <c r="G11" t="n">
-        <v>983</v>
-      </c>
-      <c r="H11" t="n">
-        <v>948</v>
-      </c>
-      <c r="I11" t="n">
-        <v>829</v>
-      </c>
-      <c r="J11" t="n">
-        <v>872</v>
-      </c>
-      <c r="K11" t="n">
-        <v>824</v>
-      </c>
       <c r="L11" t="n">
-        <v>860.4</v>
+        <v>925</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>768</v>
+        <v>974</v>
       </c>
       <c r="C12" t="n">
-        <v>820</v>
+        <v>915</v>
       </c>
       <c r="D12" t="n">
-        <v>895</v>
+        <v>919</v>
       </c>
       <c r="E12" t="n">
-        <v>918</v>
+        <v>928</v>
       </c>
       <c r="F12" t="n">
-        <v>947</v>
+        <v>925</v>
       </c>
       <c r="G12" t="n">
-        <v>902</v>
+        <v>925</v>
       </c>
       <c r="H12" t="n">
-        <v>912</v>
+        <v>877</v>
       </c>
       <c r="I12" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="J12" t="n">
-        <v>863</v>
+        <v>931</v>
       </c>
       <c r="K12" t="n">
-        <v>969</v>
+        <v>993</v>
       </c>
       <c r="L12" t="n">
-        <v>894.4</v>
+        <v>935.7</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>745</v>
+        <v>902</v>
       </c>
       <c r="C13" t="n">
-        <v>991</v>
+        <v>864</v>
       </c>
       <c r="D13" t="n">
-        <v>830</v>
+        <v>927</v>
       </c>
       <c r="E13" t="n">
-        <v>867</v>
+        <v>958</v>
       </c>
       <c r="F13" t="n">
-        <v>787</v>
+        <v>898</v>
       </c>
       <c r="G13" t="n">
-        <v>1023</v>
+        <v>899</v>
       </c>
       <c r="H13" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="I13" t="n">
-        <v>948</v>
+        <v>873</v>
       </c>
       <c r="J13" t="n">
-        <v>857</v>
+        <v>998</v>
       </c>
       <c r="K13" t="n">
-        <v>902</v>
+        <v>953</v>
       </c>
       <c r="L13" t="n">
-        <v>883.9</v>
+        <v>916.2</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>1023</v>
+        <v>928</v>
       </c>
       <c r="C14" t="n">
-        <v>890</v>
+        <v>939</v>
       </c>
       <c r="D14" t="n">
-        <v>923</v>
+        <v>945</v>
       </c>
       <c r="E14" t="n">
-        <v>1061</v>
+        <v>986</v>
       </c>
       <c r="F14" t="n">
-        <v>1086</v>
+        <v>965</v>
       </c>
       <c r="G14" t="n">
-        <v>1007</v>
+        <v>921</v>
       </c>
       <c r="H14" t="n">
-        <v>886</v>
+        <v>967</v>
       </c>
       <c r="I14" t="n">
-        <v>1041</v>
+        <v>927</v>
       </c>
       <c r="J14" t="n">
-        <v>940</v>
+        <v>1002</v>
       </c>
       <c r="K14" t="n">
-        <v>900</v>
+        <v>1056</v>
       </c>
       <c r="L14" t="n">
-        <v>975.7</v>
+        <v>963.6</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>926</v>
+        <v>1182</v>
       </c>
       <c r="C15" t="n">
-        <v>1003</v>
+        <v>942</v>
       </c>
       <c r="D15" t="n">
-        <v>969</v>
+        <v>873</v>
       </c>
       <c r="E15" t="n">
-        <v>942</v>
+        <v>932</v>
       </c>
       <c r="F15" t="n">
-        <v>987</v>
+        <v>1006</v>
       </c>
       <c r="G15" t="n">
-        <v>894</v>
+        <v>876</v>
       </c>
       <c r="H15" t="n">
-        <v>927</v>
+        <v>936</v>
       </c>
       <c r="I15" t="n">
-        <v>914</v>
+        <v>863</v>
       </c>
       <c r="J15" t="n">
-        <v>1010</v>
+        <v>999</v>
       </c>
       <c r="K15" t="n">
-        <v>1043</v>
+        <v>905</v>
       </c>
       <c r="L15" t="n">
-        <v>961.5</v>
+        <v>951.4</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="C16" t="n">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D16" t="n">
-        <v>961</v>
+        <v>885</v>
       </c>
       <c r="E16" t="n">
-        <v>963</v>
+        <v>839</v>
       </c>
       <c r="F16" t="n">
-        <v>914</v>
+        <v>945</v>
       </c>
       <c r="G16" t="n">
-        <v>926</v>
+        <v>799</v>
       </c>
       <c r="H16" t="n">
-        <v>820</v>
+        <v>889</v>
       </c>
       <c r="I16" t="n">
-        <v>1017</v>
+        <v>855</v>
       </c>
       <c r="J16" t="n">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="K16" t="n">
-        <v>1009</v>
+        <v>885</v>
       </c>
       <c r="L16" t="n">
-        <v>928.1</v>
+        <v>875.4</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>808</v>
+        <v>755</v>
       </c>
       <c r="C17" t="n">
-        <v>825</v>
+        <v>924</v>
       </c>
       <c r="D17" t="n">
-        <v>733</v>
+        <v>802</v>
       </c>
       <c r="E17" t="n">
-        <v>848</v>
+        <v>692</v>
       </c>
       <c r="F17" t="n">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="G17" t="n">
-        <v>875</v>
+        <v>828</v>
       </c>
       <c r="H17" t="n">
-        <v>753</v>
+        <v>820</v>
       </c>
       <c r="I17" t="n">
-        <v>755</v>
+        <v>827</v>
       </c>
       <c r="J17" t="n">
-        <v>853</v>
+        <v>886</v>
       </c>
       <c r="K17" t="n">
-        <v>851</v>
+        <v>869</v>
       </c>
       <c r="L17" t="n">
-        <v>806.5</v>
+        <v>815.9</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>986</v>
+        <v>953</v>
       </c>
       <c r="C18" t="n">
-        <v>872</v>
+        <v>1011</v>
       </c>
       <c r="D18" t="n">
-        <v>945</v>
+        <v>894</v>
       </c>
       <c r="E18" t="n">
-        <v>1021</v>
+        <v>1075</v>
       </c>
       <c r="F18" t="n">
-        <v>928</v>
+        <v>1022</v>
       </c>
       <c r="G18" t="n">
-        <v>960</v>
+        <v>1073</v>
       </c>
       <c r="H18" t="n">
-        <v>967</v>
+        <v>1000</v>
       </c>
       <c r="I18" t="n">
-        <v>1048</v>
+        <v>896</v>
       </c>
       <c r="J18" t="n">
-        <v>943</v>
+        <v>962</v>
       </c>
       <c r="K18" t="n">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="L18" t="n">
-        <v>961.3</v>
+        <v>983.5</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>771</v>
+        <v>960</v>
       </c>
       <c r="C19" t="n">
-        <v>866</v>
+        <v>769</v>
       </c>
       <c r="D19" t="n">
-        <v>859</v>
+        <v>914</v>
       </c>
       <c r="E19" t="n">
-        <v>821</v>
+        <v>916</v>
       </c>
       <c r="F19" t="n">
-        <v>766</v>
+        <v>930</v>
       </c>
       <c r="G19" t="n">
-        <v>793</v>
+        <v>815</v>
       </c>
       <c r="H19" t="n">
-        <v>794</v>
+        <v>827</v>
       </c>
       <c r="I19" t="n">
-        <v>819</v>
+        <v>914</v>
       </c>
       <c r="J19" t="n">
-        <v>794</v>
+        <v>878</v>
       </c>
       <c r="K19" t="n">
-        <v>831</v>
+        <v>1117</v>
       </c>
       <c r="L19" t="n">
-        <v>811.4</v>
+        <v>904</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
+        <v>836</v>
+      </c>
+      <c r="C20" t="n">
+        <v>789</v>
+      </c>
+      <c r="D20" t="n">
+        <v>855</v>
+      </c>
+      <c r="E20" t="n">
+        <v>888</v>
+      </c>
+      <c r="F20" t="n">
+        <v>796</v>
+      </c>
+      <c r="G20" t="n">
+        <v>818</v>
+      </c>
+      <c r="H20" t="n">
+        <v>940</v>
+      </c>
+      <c r="I20" t="n">
+        <v>848</v>
+      </c>
+      <c r="J20" t="n">
         <v>838</v>
       </c>
-      <c r="C20" t="n">
-        <v>702</v>
-      </c>
-      <c r="D20" t="n">
-        <v>875</v>
-      </c>
-      <c r="E20" t="n">
-        <v>874</v>
-      </c>
-      <c r="F20" t="n">
-        <v>752</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="K20" t="n">
         <v>852</v>
       </c>
-      <c r="H20" t="n">
-        <v>752</v>
-      </c>
-      <c r="I20" t="n">
-        <v>857</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>846</v>
-      </c>
-      <c r="K20" t="n">
-        <v>889</v>
-      </c>
-      <c r="L20" t="n">
-        <v>823.7</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="C21" t="n">
-        <v>829</v>
+        <v>924</v>
       </c>
       <c r="D21" t="n">
-        <v>956</v>
+        <v>1023</v>
       </c>
       <c r="E21" t="n">
-        <v>847</v>
+        <v>914</v>
       </c>
       <c r="F21" t="n">
-        <v>853</v>
+        <v>954</v>
       </c>
       <c r="G21" t="n">
-        <v>948</v>
+        <v>985</v>
       </c>
       <c r="H21" t="n">
-        <v>866</v>
+        <v>901</v>
       </c>
       <c r="I21" t="n">
-        <v>904</v>
+        <v>992</v>
       </c>
       <c r="J21" t="n">
-        <v>1014</v>
+        <v>1060</v>
       </c>
       <c r="K21" t="n">
-        <v>924</v>
+        <v>958</v>
       </c>
       <c r="L21" t="n">
-        <v>904.1</v>
+        <v>963.2</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>893</v>
+        <v>863</v>
       </c>
       <c r="C22" t="n">
-        <v>944</v>
+        <v>914</v>
       </c>
       <c r="D22" t="n">
-        <v>903</v>
+        <v>820</v>
       </c>
       <c r="E22" t="n">
-        <v>917</v>
+        <v>820</v>
       </c>
       <c r="F22" t="n">
-        <v>1091</v>
+        <v>873</v>
       </c>
       <c r="G22" t="n">
-        <v>841</v>
+        <v>820</v>
       </c>
       <c r="H22" t="n">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="I22" t="n">
-        <v>869</v>
+        <v>778</v>
       </c>
       <c r="J22" t="n">
-        <v>893</v>
+        <v>1037</v>
       </c>
       <c r="K22" t="n">
-        <v>880</v>
+        <v>927</v>
       </c>
       <c r="L22" t="n">
-        <v>908</v>
+        <v>869.4</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
+        <v>980</v>
+      </c>
+      <c r="C23" t="n">
+        <v>993</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1079</v>
+      </c>
+      <c r="E23" t="n">
+        <v>894</v>
+      </c>
+      <c r="F23" t="n">
+        <v>922</v>
+      </c>
+      <c r="G23" t="n">
         <v>954</v>
       </c>
-      <c r="C23" t="n">
-        <v>877</v>
-      </c>
-      <c r="D23" t="n">
-        <v>960</v>
-      </c>
-      <c r="E23" t="n">
-        <v>989</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1003</v>
-      </c>
-      <c r="G23" t="n">
-        <v>986</v>
-      </c>
       <c r="H23" t="n">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="I23" t="n">
-        <v>842</v>
+        <v>902</v>
       </c>
       <c r="J23" t="n">
-        <v>896</v>
+        <v>923</v>
       </c>
       <c r="K23" t="n">
-        <v>923</v>
+        <v>872</v>
       </c>
       <c r="L23" t="n">
-        <v>927.8</v>
+        <v>936.5</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="C24" t="n">
-        <v>758</v>
+        <v>906</v>
       </c>
       <c r="D24" t="n">
-        <v>860</v>
+        <v>892</v>
       </c>
       <c r="E24" t="n">
-        <v>1007</v>
+        <v>918</v>
       </c>
       <c r="F24" t="n">
-        <v>772</v>
+        <v>951</v>
       </c>
       <c r="G24" t="n">
-        <v>796</v>
+        <v>748</v>
       </c>
       <c r="H24" t="n">
-        <v>798</v>
+        <v>807</v>
       </c>
       <c r="I24" t="n">
-        <v>854</v>
+        <v>993</v>
       </c>
       <c r="J24" t="n">
-        <v>913</v>
+        <v>866</v>
       </c>
       <c r="K24" t="n">
-        <v>929</v>
+        <v>844</v>
       </c>
       <c r="L24" t="n">
-        <v>853</v>
+        <v>877.7</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>861</v>
+        <v>1124</v>
       </c>
       <c r="C25" t="n">
-        <v>952</v>
+        <v>987</v>
       </c>
       <c r="D25" t="n">
-        <v>870</v>
+        <v>948</v>
       </c>
       <c r="E25" t="n">
-        <v>880</v>
+        <v>896</v>
       </c>
       <c r="F25" t="n">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="G25" t="n">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="H25" t="n">
-        <v>836</v>
+        <v>936</v>
       </c>
       <c r="I25" t="n">
-        <v>953</v>
+        <v>994</v>
       </c>
       <c r="J25" t="n">
-        <v>838</v>
+        <v>883</v>
       </c>
       <c r="K25" t="n">
-        <v>909</v>
+        <v>935</v>
       </c>
       <c r="L25" t="n">
-        <v>906</v>
+        <v>967.2</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>898</v>
+        <v>951</v>
       </c>
       <c r="C26" t="n">
-        <v>1113</v>
+        <v>1007</v>
       </c>
       <c r="D26" t="n">
-        <v>1045</v>
+        <v>871</v>
       </c>
       <c r="E26" t="n">
-        <v>1057</v>
+        <v>932</v>
       </c>
       <c r="F26" t="n">
-        <v>993</v>
+        <v>1166</v>
       </c>
       <c r="G26" t="n">
-        <v>1106</v>
+        <v>1049</v>
       </c>
       <c r="H26" t="n">
-        <v>971</v>
+        <v>1038</v>
       </c>
       <c r="I26" t="n">
-        <v>896</v>
+        <v>982</v>
       </c>
       <c r="J26" t="n">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>978</v>
       </c>
       <c r="L26" t="n">
-        <v>1005.4</v>
+        <v>994.1</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1029</v>
+        <v>1011</v>
       </c>
       <c r="C27" t="n">
-        <v>938</v>
+        <v>955</v>
       </c>
       <c r="D27" t="n">
-        <v>963</v>
+        <v>988</v>
       </c>
       <c r="E27" t="n">
-        <v>943</v>
+        <v>918</v>
       </c>
       <c r="F27" t="n">
-        <v>999</v>
+        <v>878</v>
       </c>
       <c r="G27" t="n">
-        <v>986</v>
+        <v>928</v>
       </c>
       <c r="H27" t="n">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="I27" t="n">
-        <v>930</v>
+        <v>1119</v>
       </c>
       <c r="J27" t="n">
-        <v>938</v>
+        <v>981</v>
       </c>
       <c r="K27" t="n">
-        <v>949</v>
+        <v>1015</v>
       </c>
       <c r="L27" t="n">
-        <v>960.9</v>
+        <v>972.4</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C28" t="n">
-        <v>852</v>
+        <v>832</v>
       </c>
       <c r="D28" t="n">
-        <v>844</v>
+        <v>797</v>
       </c>
       <c r="E28" t="n">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="F28" t="n">
-        <v>796</v>
+        <v>867</v>
       </c>
       <c r="G28" t="n">
-        <v>935</v>
+        <v>783</v>
       </c>
       <c r="H28" t="n">
-        <v>817</v>
+        <v>1045</v>
       </c>
       <c r="I28" t="n">
-        <v>811</v>
+        <v>797</v>
       </c>
       <c r="J28" t="n">
-        <v>873</v>
+        <v>816</v>
       </c>
       <c r="K28" t="n">
-        <v>928</v>
+        <v>838</v>
       </c>
       <c r="L28" t="n">
-        <v>857</v>
+        <v>848.9</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>807</v>
+        <v>882</v>
       </c>
       <c r="C29" t="n">
-        <v>875</v>
+        <v>918</v>
       </c>
       <c r="D29" t="n">
-        <v>785</v>
+        <v>864</v>
       </c>
       <c r="E29" t="n">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="F29" t="n">
-        <v>844</v>
+        <v>940</v>
       </c>
       <c r="G29" t="n">
-        <v>827</v>
+        <v>947</v>
       </c>
       <c r="H29" t="n">
-        <v>758</v>
+        <v>951</v>
       </c>
       <c r="I29" t="n">
-        <v>805</v>
+        <v>887</v>
       </c>
       <c r="J29" t="n">
-        <v>911</v>
+        <v>874</v>
       </c>
       <c r="K29" t="n">
-        <v>797</v>
+        <v>960</v>
       </c>
       <c r="L29" t="n">
-        <v>831.4</v>
+        <v>913.4</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>812</v>
+        <v>932</v>
       </c>
       <c r="C30" t="n">
-        <v>914</v>
+        <v>885</v>
       </c>
       <c r="D30" t="n">
+        <v>1006</v>
+      </c>
+      <c r="E30" t="n">
         <v>868</v>
       </c>
-      <c r="E30" t="n">
-        <v>813</v>
-      </c>
       <c r="F30" t="n">
-        <v>907</v>
+        <v>962</v>
       </c>
       <c r="G30" t="n">
-        <v>862</v>
+        <v>936</v>
       </c>
       <c r="H30" t="n">
-        <v>799</v>
+        <v>899</v>
       </c>
       <c r="I30" t="n">
-        <v>998</v>
+        <v>912</v>
       </c>
       <c r="J30" t="n">
-        <v>833</v>
+        <v>817</v>
       </c>
       <c r="K30" t="n">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="L30" t="n">
-        <v>868.4</v>
+        <v>909</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>927</v>
+        <v>1007</v>
       </c>
       <c r="C31" t="n">
-        <v>860</v>
+        <v>924</v>
       </c>
       <c r="D31" t="n">
-        <v>908</v>
+        <v>1035</v>
       </c>
       <c r="E31" t="n">
-        <v>940</v>
+        <v>978</v>
       </c>
       <c r="F31" t="n">
-        <v>798</v>
+        <v>899</v>
       </c>
       <c r="G31" t="n">
-        <v>922</v>
+        <v>830</v>
       </c>
       <c r="H31" t="n">
-        <v>793</v>
+        <v>900</v>
       </c>
       <c r="I31" t="n">
-        <v>902</v>
+        <v>967</v>
       </c>
       <c r="J31" t="n">
-        <v>950</v>
+        <v>959</v>
       </c>
       <c r="K31" t="n">
-        <v>976</v>
+        <v>895</v>
       </c>
       <c r="L31" t="n">
-        <v>897.6</v>
+        <v>939.4</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="C32" t="n">
-        <v>1007</v>
+        <v>946</v>
       </c>
       <c r="D32" t="n">
-        <v>1031</v>
+        <v>978</v>
       </c>
       <c r="E32" t="n">
-        <v>971</v>
+        <v>995</v>
       </c>
       <c r="F32" t="n">
+        <v>955</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1026</v>
+      </c>
+      <c r="H32" t="n">
         <v>1034</v>
       </c>
-      <c r="G32" t="n">
-        <v>1220</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1103</v>
-      </c>
       <c r="I32" t="n">
-        <v>1029</v>
+        <v>979</v>
       </c>
       <c r="J32" t="n">
-        <v>994</v>
+        <v>1111</v>
       </c>
       <c r="K32" t="n">
-        <v>1082</v>
+        <v>944</v>
       </c>
       <c r="L32" t="n">
-        <v>1055.4</v>
+        <v>1005.7</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>831</v>
+        <v>924</v>
       </c>
       <c r="C33" t="n">
-        <v>906</v>
+        <v>883</v>
       </c>
       <c r="D33" t="n">
-        <v>896</v>
+        <v>740</v>
       </c>
       <c r="E33" t="n">
-        <v>999</v>
+        <v>916</v>
       </c>
       <c r="F33" t="n">
-        <v>1048</v>
+        <v>879</v>
       </c>
       <c r="G33" t="n">
-        <v>863</v>
+        <v>913</v>
       </c>
       <c r="H33" t="n">
-        <v>1009</v>
+        <v>836</v>
       </c>
       <c r="I33" t="n">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="J33" t="n">
-        <v>953</v>
+        <v>856</v>
       </c>
       <c r="K33" t="n">
-        <v>838</v>
+        <v>859</v>
       </c>
       <c r="L33" t="n">
-        <v>923.1</v>
+        <v>871.3</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>858</v>
+        <v>966</v>
       </c>
       <c r="C34" t="n">
-        <v>933</v>
+        <v>914</v>
       </c>
       <c r="D34" t="n">
-        <v>1127</v>
+        <v>981</v>
       </c>
       <c r="E34" t="n">
-        <v>866</v>
+        <v>917</v>
       </c>
       <c r="F34" t="n">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="G34" t="n">
-        <v>960</v>
+        <v>983</v>
       </c>
       <c r="H34" t="n">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="I34" t="n">
-        <v>929</v>
+        <v>912</v>
       </c>
       <c r="J34" t="n">
-        <v>998</v>
+        <v>893</v>
       </c>
       <c r="K34" t="n">
-        <v>918</v>
+        <v>997</v>
       </c>
       <c r="L34" t="n">
-        <v>945.1</v>
+        <v>943.1</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>873</v>
+        <v>857</v>
       </c>
       <c r="C35" t="n">
-        <v>1023</v>
+        <v>903</v>
       </c>
       <c r="D35" t="n">
-        <v>1096</v>
+        <v>845</v>
       </c>
       <c r="E35" t="n">
-        <v>946</v>
+        <v>906</v>
       </c>
       <c r="F35" t="n">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="G35" t="n">
-        <v>918</v>
+        <v>982</v>
       </c>
       <c r="H35" t="n">
-        <v>1028</v>
+        <v>863</v>
       </c>
       <c r="I35" t="n">
-        <v>876</v>
+        <v>855</v>
       </c>
       <c r="J35" t="n">
-        <v>1022</v>
+        <v>850</v>
       </c>
       <c r="K35" t="n">
-        <v>885</v>
+        <v>948</v>
       </c>
       <c r="L35" t="n">
-        <v>956.6</v>
+        <v>891.2</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>996</v>
+        <v>976</v>
       </c>
       <c r="C36" t="n">
-        <v>952</v>
+        <v>1046</v>
       </c>
       <c r="D36" t="n">
-        <v>849</v>
+        <v>992</v>
       </c>
       <c r="E36" t="n">
-        <v>933</v>
+        <v>956</v>
       </c>
       <c r="F36" t="n">
-        <v>815</v>
+        <v>1045</v>
       </c>
       <c r="G36" t="n">
-        <v>824</v>
+        <v>944</v>
       </c>
       <c r="H36" t="n">
-        <v>983</v>
+        <v>915</v>
       </c>
       <c r="I36" t="n">
-        <v>888</v>
+        <v>954</v>
       </c>
       <c r="J36" t="n">
-        <v>993</v>
+        <v>944</v>
       </c>
       <c r="K36" t="n">
-        <v>970</v>
+        <v>850</v>
       </c>
       <c r="L36" t="n">
-        <v>920.3</v>
+        <v>962.2</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>825</v>
+        <v>868</v>
       </c>
       <c r="C37" t="n">
-        <v>841</v>
+        <v>774</v>
       </c>
       <c r="D37" t="n">
-        <v>955</v>
+        <v>882</v>
       </c>
       <c r="E37" t="n">
-        <v>882</v>
+        <v>925</v>
       </c>
       <c r="F37" t="n">
-        <v>858</v>
+        <v>928</v>
       </c>
       <c r="G37" t="n">
-        <v>948</v>
+        <v>856</v>
       </c>
       <c r="H37" t="n">
-        <v>887</v>
+        <v>749</v>
       </c>
       <c r="I37" t="n">
-        <v>984</v>
+        <v>910</v>
       </c>
       <c r="J37" t="n">
-        <v>822</v>
+        <v>801</v>
       </c>
       <c r="K37" t="n">
-        <v>916</v>
+        <v>892</v>
       </c>
       <c r="L37" t="n">
-        <v>891.8</v>
+        <v>858.5</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="C38" t="n">
-        <v>924</v>
+        <v>857</v>
       </c>
       <c r="D38" t="n">
-        <v>833</v>
+        <v>1005</v>
       </c>
       <c r="E38" t="n">
-        <v>915</v>
+        <v>851</v>
       </c>
       <c r="F38" t="n">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="G38" t="n">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H38" t="n">
-        <v>887</v>
+        <v>849</v>
       </c>
       <c r="I38" t="n">
-        <v>793</v>
+        <v>882</v>
       </c>
       <c r="J38" t="n">
-        <v>885</v>
+        <v>851</v>
       </c>
       <c r="K38" t="n">
-        <v>755</v>
+        <v>856</v>
       </c>
       <c r="L38" t="n">
-        <v>855.8</v>
+        <v>869.3</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>841</v>
+        <v>888</v>
       </c>
       <c r="C39" t="n">
-        <v>836</v>
+        <v>896</v>
       </c>
       <c r="D39" t="n">
-        <v>852</v>
+        <v>889</v>
       </c>
       <c r="E39" t="n">
-        <v>911</v>
+        <v>813</v>
       </c>
       <c r="F39" t="n">
-        <v>889</v>
+        <v>920</v>
       </c>
       <c r="G39" t="n">
-        <v>920</v>
+        <v>965</v>
       </c>
       <c r="H39" t="n">
-        <v>865</v>
+        <v>958</v>
       </c>
       <c r="I39" t="n">
-        <v>835</v>
+        <v>928</v>
       </c>
       <c r="J39" t="n">
-        <v>822</v>
+        <v>883</v>
       </c>
       <c r="K39" t="n">
-        <v>887</v>
+        <v>971</v>
       </c>
       <c r="L39" t="n">
-        <v>865.8</v>
+        <v>911.1</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>890</v>
+        <v>853</v>
       </c>
       <c r="C40" t="n">
-        <v>882</v>
+        <v>802</v>
       </c>
       <c r="D40" t="n">
-        <v>872</v>
+        <v>894</v>
       </c>
       <c r="E40" t="n">
-        <v>867</v>
+        <v>846</v>
       </c>
       <c r="F40" t="n">
-        <v>846</v>
+        <v>898</v>
       </c>
       <c r="G40" t="n">
-        <v>859</v>
+        <v>875</v>
       </c>
       <c r="H40" t="n">
-        <v>871</v>
+        <v>908</v>
       </c>
       <c r="I40" t="n">
-        <v>880</v>
+        <v>862</v>
       </c>
       <c r="J40" t="n">
-        <v>898</v>
+        <v>751</v>
       </c>
       <c r="K40" t="n">
-        <v>799</v>
+        <v>827</v>
       </c>
       <c r="L40" t="n">
-        <v>866.4</v>
+        <v>851.6</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>886</v>
+        <v>853</v>
       </c>
       <c r="C41" t="n">
-        <v>720</v>
+        <v>798</v>
       </c>
       <c r="D41" t="n">
-        <v>939</v>
+        <v>952</v>
       </c>
       <c r="E41" t="n">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="F41" t="n">
-        <v>783</v>
+        <v>900</v>
       </c>
       <c r="G41" t="n">
-        <v>889</v>
+        <v>741</v>
       </c>
       <c r="H41" t="n">
-        <v>757</v>
+        <v>772</v>
       </c>
       <c r="I41" t="n">
-        <v>895</v>
+        <v>860</v>
       </c>
       <c r="J41" t="n">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="K41" t="n">
-        <v>775</v>
+        <v>864</v>
       </c>
       <c r="L41" t="n">
-        <v>819.4</v>
+        <v>828.5</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>953</v>
+        <v>932</v>
       </c>
       <c r="C42" t="n">
-        <v>884</v>
+        <v>928</v>
       </c>
       <c r="D42" t="n">
-        <v>942</v>
+        <v>857</v>
       </c>
       <c r="E42" t="n">
+        <v>854</v>
+      </c>
+      <c r="F42" t="n">
+        <v>879</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1007</v>
+      </c>
+      <c r="H42" t="n">
+        <v>793</v>
+      </c>
+      <c r="I42" t="n">
+        <v>825</v>
+      </c>
+      <c r="J42" t="n">
         <v>838</v>
       </c>
-      <c r="F42" t="n">
-        <v>919</v>
-      </c>
-      <c r="G42" t="n">
-        <v>866</v>
-      </c>
-      <c r="H42" t="n">
-        <v>847</v>
-      </c>
-      <c r="I42" t="n">
-        <v>969</v>
-      </c>
-      <c r="J42" t="n">
-        <v>803</v>
-      </c>
       <c r="K42" t="n">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="L42" t="n">
-        <v>880.1</v>
+        <v>870.3</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>890</v>
+        <v>807</v>
       </c>
       <c r="C43" t="n">
+        <v>833</v>
+      </c>
+      <c r="D43" t="n">
         <v>898</v>
       </c>
-      <c r="D43" t="n">
-        <v>821</v>
-      </c>
       <c r="E43" t="n">
-        <v>856</v>
+        <v>811</v>
       </c>
       <c r="F43" t="n">
-        <v>971</v>
+        <v>876</v>
       </c>
       <c r="G43" t="n">
-        <v>844</v>
+        <v>969</v>
       </c>
       <c r="H43" t="n">
-        <v>837</v>
+        <v>903</v>
       </c>
       <c r="I43" t="n">
-        <v>992</v>
+        <v>945</v>
       </c>
       <c r="J43" t="n">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="K43" t="n">
-        <v>977</v>
+        <v>804</v>
       </c>
       <c r="L43" t="n">
-        <v>897.4</v>
+        <v>872.6</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>786</v>
+        <v>824</v>
       </c>
       <c r="C44" t="n">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D44" t="n">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="E44" t="n">
-        <v>785</v>
+        <v>808</v>
       </c>
       <c r="F44" t="n">
-        <v>707</v>
+        <v>863</v>
       </c>
       <c r="G44" t="n">
-        <v>817</v>
+        <v>754</v>
       </c>
       <c r="H44" t="n">
-        <v>745</v>
+        <v>849</v>
       </c>
       <c r="I44" t="n">
-        <v>877</v>
+        <v>827</v>
       </c>
       <c r="J44" t="n">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="K44" t="n">
-        <v>797</v>
+        <v>770</v>
       </c>
       <c r="L44" t="n">
-        <v>793.7</v>
+        <v>811.4</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1242</v>
+        <v>1055</v>
       </c>
       <c r="C45" t="n">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D45" t="n">
-        <v>955</v>
+        <v>896</v>
       </c>
       <c r="E45" t="n">
-        <v>1064</v>
+        <v>1035</v>
       </c>
       <c r="F45" t="n">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="G45" t="n">
-        <v>1138</v>
+        <v>1071</v>
       </c>
       <c r="H45" t="n">
-        <v>939</v>
+        <v>1026</v>
       </c>
       <c r="I45" t="n">
-        <v>989</v>
+        <v>1042</v>
       </c>
       <c r="J45" t="n">
-        <v>1006</v>
+        <v>945</v>
       </c>
       <c r="K45" t="n">
-        <v>974</v>
+        <v>902</v>
       </c>
       <c r="L45" t="n">
-        <v>1030.6</v>
+        <v>997.4</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>908</v>
+        <v>975</v>
       </c>
       <c r="C46" t="n">
-        <v>929</v>
+        <v>942</v>
       </c>
       <c r="D46" t="n">
-        <v>844</v>
+        <v>882</v>
       </c>
       <c r="E46" t="n">
-        <v>954</v>
+        <v>884</v>
       </c>
       <c r="F46" t="n">
-        <v>1009</v>
+        <v>910</v>
       </c>
       <c r="G46" t="n">
-        <v>885</v>
+        <v>866</v>
       </c>
       <c r="H46" t="n">
-        <v>886</v>
+        <v>806</v>
       </c>
       <c r="I46" t="n">
-        <v>936</v>
+        <v>863</v>
       </c>
       <c r="J46" t="n">
-        <v>892</v>
+        <v>878</v>
       </c>
       <c r="K46" t="n">
-        <v>1026</v>
+        <v>836</v>
       </c>
       <c r="L46" t="n">
-        <v>926.9</v>
+        <v>884.2</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>907</v>
+        <v>993</v>
       </c>
       <c r="C47" t="n">
-        <v>887</v>
+        <v>941</v>
       </c>
       <c r="D47" t="n">
-        <v>1085</v>
+        <v>1070</v>
       </c>
       <c r="E47" t="n">
-        <v>979</v>
+        <v>1042</v>
       </c>
       <c r="F47" t="n">
+        <v>990</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1162</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1214</v>
+      </c>
+      <c r="I47" t="n">
+        <v>936</v>
+      </c>
+      <c r="J47" t="n">
         <v>978</v>
       </c>
-      <c r="G47" t="n">
-        <v>1080</v>
-      </c>
-      <c r="H47" t="n">
-        <v>988</v>
-      </c>
-      <c r="I47" t="n">
-        <v>982</v>
-      </c>
-      <c r="J47" t="n">
-        <v>842</v>
-      </c>
       <c r="K47" t="n">
-        <v>985</v>
+        <v>1082</v>
       </c>
       <c r="L47" t="n">
-        <v>971.3</v>
+        <v>1040.8</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>750</v>
+        <v>772</v>
       </c>
       <c r="C48" t="n">
-        <v>779</v>
+        <v>708</v>
       </c>
       <c r="D48" t="n">
-        <v>764</v>
+        <v>744</v>
       </c>
       <c r="E48" t="n">
-        <v>881</v>
+        <v>773</v>
       </c>
       <c r="F48" t="n">
-        <v>797</v>
+        <v>697</v>
       </c>
       <c r="G48" t="n">
-        <v>764</v>
+        <v>710</v>
       </c>
       <c r="H48" t="n">
-        <v>730</v>
+        <v>669</v>
       </c>
       <c r="I48" t="n">
-        <v>791</v>
+        <v>749</v>
       </c>
       <c r="J48" t="n">
-        <v>827</v>
+        <v>735</v>
       </c>
       <c r="K48" t="n">
-        <v>742</v>
+        <v>677</v>
       </c>
       <c r="L48" t="n">
-        <v>782.5</v>
+        <v>723.4</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>816</v>
+        <v>865</v>
       </c>
       <c r="C49" t="n">
-        <v>934</v>
+        <v>976</v>
       </c>
       <c r="D49" t="n">
-        <v>1019</v>
+        <v>946</v>
       </c>
       <c r="E49" t="n">
-        <v>936</v>
+        <v>769</v>
       </c>
       <c r="F49" t="n">
-        <v>928</v>
+        <v>887</v>
       </c>
       <c r="G49" t="n">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="H49" t="n">
-        <v>1004</v>
+        <v>972</v>
       </c>
       <c r="I49" t="n">
-        <v>845</v>
+        <v>965</v>
       </c>
       <c r="J49" t="n">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="K49" t="n">
-        <v>923</v>
+        <v>957</v>
       </c>
       <c r="L49" t="n">
-        <v>919.9</v>
+        <v>916</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>915</v>
+        <v>862</v>
       </c>
       <c r="C50" t="n">
-        <v>849</v>
+        <v>906</v>
       </c>
       <c r="D50" t="n">
-        <v>773</v>
+        <v>848</v>
       </c>
       <c r="E50" t="n">
-        <v>900</v>
+        <v>951</v>
       </c>
       <c r="F50" t="n">
-        <v>939</v>
+        <v>918</v>
       </c>
       <c r="G50" t="n">
-        <v>833</v>
+        <v>819</v>
       </c>
       <c r="H50" t="n">
-        <v>978</v>
+        <v>904</v>
       </c>
       <c r="I50" t="n">
-        <v>811</v>
+        <v>972</v>
       </c>
       <c r="J50" t="n">
-        <v>968</v>
+        <v>896</v>
       </c>
       <c r="K50" t="n">
-        <v>775</v>
+        <v>808</v>
       </c>
       <c r="L50" t="n">
-        <v>874.1</v>
+        <v>888.4</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>883</v>
+        <v>914</v>
       </c>
       <c r="C51" t="n">
-        <v>924</v>
+        <v>861</v>
       </c>
       <c r="D51" t="n">
-        <v>912</v>
+        <v>822</v>
       </c>
       <c r="E51" t="n">
-        <v>881</v>
+        <v>914</v>
       </c>
       <c r="F51" t="n">
-        <v>910</v>
+        <v>835</v>
       </c>
       <c r="G51" t="n">
-        <v>926</v>
+        <v>858</v>
       </c>
       <c r="H51" t="n">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="I51" t="n">
-        <v>917</v>
+        <v>936</v>
       </c>
       <c r="J51" t="n">
-        <v>927</v>
+        <v>851</v>
       </c>
       <c r="K51" t="n">
-        <v>881</v>
+        <v>967</v>
       </c>
       <c r="L51" t="n">
-        <v>905.8</v>
+        <v>884.4</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>889.76</v>
+        <v>918.02</v>
       </c>
       <c r="C52" t="n">
-        <v>889.88</v>
+        <v>903.72</v>
       </c>
       <c r="D52" t="n">
-        <v>908.26</v>
+        <v>902.64</v>
       </c>
       <c r="E52" t="n">
-        <v>907.1799999999999</v>
+        <v>896.26</v>
       </c>
       <c r="F52" t="n">
-        <v>895.16</v>
+        <v>922.34</v>
       </c>
       <c r="G52" t="n">
-        <v>908.6799999999999</v>
+        <v>902.9</v>
       </c>
       <c r="H52" t="n">
-        <v>878.9</v>
+        <v>898.64</v>
       </c>
       <c r="I52" t="n">
-        <v>902.76</v>
+        <v>907.16</v>
       </c>
       <c r="J52" t="n">
-        <v>899.42</v>
+        <v>902.48</v>
       </c>
       <c r="K52" t="n">
-        <v>897.52</v>
+        <v>901.28</v>
       </c>
       <c r="L52" t="n">
-        <v>897.752</v>
+        <v>905.5440000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>7.205449819564819</v>
+        <v>8.973358392715454</v>
       </c>
       <c r="C2" t="n">
-        <v>8.954928398132324</v>
+        <v>8.706533432006836</v>
       </c>
       <c r="D2" t="n">
-        <v>9.17658805847168</v>
+        <v>7.824311971664429</v>
       </c>
       <c r="E2" t="n">
-        <v>8.535671472549438</v>
+        <v>7.535370826721191</v>
       </c>
       <c r="F2" t="n">
-        <v>8.505389451980591</v>
+        <v>7.205822229385376</v>
       </c>
       <c r="G2" t="n">
-        <v>9.019191980361938</v>
+        <v>7.169218301773071</v>
       </c>
       <c r="H2" t="n">
-        <v>8.438050985336304</v>
+        <v>7.105427026748657</v>
       </c>
       <c r="I2" t="n">
-        <v>8.471680641174316</v>
+        <v>7.561770915985107</v>
       </c>
       <c r="J2" t="n">
-        <v>9.758065223693848</v>
+        <v>7.188247203826904</v>
       </c>
       <c r="K2" t="n">
-        <v>8.39641809463501</v>
+        <v>7.232170581817627</v>
       </c>
       <c r="L2" t="n">
-        <v>8.646143412590027</v>
+        <v>7.650223088264466</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>9.921016454696655</v>
+        <v>7.306848287582397</v>
       </c>
       <c r="C3" t="n">
-        <v>8.308944225311279</v>
+        <v>7.270090818405151</v>
       </c>
       <c r="D3" t="n">
-        <v>10.55039715766907</v>
+        <v>7.396796703338623</v>
       </c>
       <c r="E3" t="n">
-        <v>9.688800811767578</v>
+        <v>7.415729761123657</v>
       </c>
       <c r="F3" t="n">
-        <v>8.416034460067749</v>
+        <v>7.361376762390137</v>
       </c>
       <c r="G3" t="n">
-        <v>9.416433572769165</v>
+        <v>7.366852760314941</v>
       </c>
       <c r="H3" t="n">
-        <v>9.924513339996338</v>
+        <v>8.36108136177063</v>
       </c>
       <c r="I3" t="n">
-        <v>8.148089647293091</v>
+        <v>7.60566782951355</v>
       </c>
       <c r="J3" t="n">
-        <v>8.631369590759277</v>
+        <v>7.212656259536743</v>
       </c>
       <c r="K3" t="n">
-        <v>9.510235786437988</v>
+        <v>7.272993087768555</v>
       </c>
       <c r="L3" t="n">
-        <v>9.25158350467682</v>
+        <v>7.457009363174438</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>8.672768115997314</v>
+        <v>7.951257705688477</v>
       </c>
       <c r="C4" t="n">
-        <v>8.258101463317871</v>
+        <v>8.579198837280273</v>
       </c>
       <c r="D4" t="n">
-        <v>8.380419969558716</v>
+        <v>8.232018709182739</v>
       </c>
       <c r="E4" t="n">
-        <v>8.146200656890869</v>
+        <v>7.717841148376465</v>
       </c>
       <c r="F4" t="n">
-        <v>7.875836133956909</v>
+        <v>7.396220445632935</v>
       </c>
       <c r="G4" t="n">
-        <v>8.019001483917236</v>
+        <v>7.393693447113037</v>
       </c>
       <c r="H4" t="n">
-        <v>7.915518045425415</v>
+        <v>7.506385564804077</v>
       </c>
       <c r="I4" t="n">
-        <v>9.850075960159302</v>
+        <v>7.82907509803772</v>
       </c>
       <c r="J4" t="n">
-        <v>8.21281623840332</v>
+        <v>7.250041484832764</v>
       </c>
       <c r="K4" t="n">
-        <v>7.882101058959961</v>
+        <v>7.980156898498535</v>
       </c>
       <c r="L4" t="n">
-        <v>8.321283912658691</v>
+        <v>7.783588933944702</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>7.998042583465576</v>
+        <v>7.402142763137817</v>
       </c>
       <c r="C5" t="n">
-        <v>7.447925567626953</v>
+        <v>6.770764112472534</v>
       </c>
       <c r="D5" t="n">
-        <v>7.41256856918335</v>
+        <v>6.720389366149902</v>
       </c>
       <c r="E5" t="n">
-        <v>7.659421443939209</v>
+        <v>7.416098833084106</v>
       </c>
       <c r="F5" t="n">
-        <v>7.662602186203003</v>
+        <v>7.222208499908447</v>
       </c>
       <c r="G5" t="n">
-        <v>8.197141170501709</v>
+        <v>6.978875160217285</v>
       </c>
       <c r="H5" t="n">
-        <v>8.144602060317993</v>
+        <v>7.347424745559692</v>
       </c>
       <c r="I5" t="n">
-        <v>7.810240030288696</v>
+        <v>6.727997541427612</v>
       </c>
       <c r="J5" t="n">
-        <v>7.800834178924561</v>
+        <v>7.387788057327271</v>
       </c>
       <c r="K5" t="n">
-        <v>8.489917516708374</v>
+        <v>7.449616670608521</v>
       </c>
       <c r="L5" t="n">
-        <v>7.862329530715942</v>
+        <v>7.142330574989319</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>8.215359687805176</v>
+        <v>7.634152173995972</v>
       </c>
       <c r="C6" t="n">
-        <v>8.764752864837646</v>
+        <v>7.739893198013306</v>
       </c>
       <c r="D6" t="n">
-        <v>7.962844133377075</v>
+        <v>7.144922256469727</v>
       </c>
       <c r="E6" t="n">
-        <v>7.758062839508057</v>
+        <v>7.072061061859131</v>
       </c>
       <c r="F6" t="n">
-        <v>8.879015207290649</v>
+        <v>7.883262872695923</v>
       </c>
       <c r="G6" t="n">
-        <v>8.107741832733154</v>
+        <v>7.118062973022461</v>
       </c>
       <c r="H6" t="n">
-        <v>8.575824737548828</v>
+        <v>7.500455141067505</v>
       </c>
       <c r="I6" t="n">
-        <v>7.937777042388916</v>
+        <v>7.26242470741272</v>
       </c>
       <c r="J6" t="n">
-        <v>9.216420888900757</v>
+        <v>7.894417285919189</v>
       </c>
       <c r="K6" t="n">
-        <v>8.093331575393677</v>
+        <v>7.888463973999023</v>
       </c>
       <c r="L6" t="n">
-        <v>8.351113080978394</v>
+        <v>7.513811564445495</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>8.572674989700317</v>
+        <v>7.724887847900391</v>
       </c>
       <c r="C7" t="n">
-        <v>9.727531433105469</v>
+        <v>7.547261476516724</v>
       </c>
       <c r="D7" t="n">
-        <v>8.463982582092285</v>
+        <v>8.049008846282959</v>
       </c>
       <c r="E7" t="n">
-        <v>9.106606245040894</v>
+        <v>7.372729539871216</v>
       </c>
       <c r="F7" t="n">
-        <v>8.695148468017578</v>
+        <v>7.567765235900879</v>
       </c>
       <c r="G7" t="n">
-        <v>8.555927991867065</v>
+        <v>7.538324594497681</v>
       </c>
       <c r="H7" t="n">
-        <v>8.012476682662964</v>
+        <v>7.587614297866821</v>
       </c>
       <c r="I7" t="n">
-        <v>8.979568481445312</v>
+        <v>8.141475200653076</v>
       </c>
       <c r="J7" t="n">
-        <v>8.166449785232544</v>
+        <v>7.733396291732788</v>
       </c>
       <c r="K7" t="n">
-        <v>8.525495052337646</v>
+        <v>7.12495756149292</v>
       </c>
       <c r="L7" t="n">
-        <v>8.680586171150207</v>
+        <v>7.638742089271545</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>8.927007436752319</v>
+        <v>7.600248575210571</v>
       </c>
       <c r="C8" t="n">
-        <v>7.531928062438965</v>
+        <v>8.332846403121948</v>
       </c>
       <c r="D8" t="n">
-        <v>8.45631217956543</v>
+        <v>7.258133172988892</v>
       </c>
       <c r="E8" t="n">
-        <v>7.935814619064331</v>
+        <v>7.403547048568726</v>
       </c>
       <c r="F8" t="n">
-        <v>7.337672472000122</v>
+        <v>8.063501834869385</v>
       </c>
       <c r="G8" t="n">
-        <v>7.984778642654419</v>
+        <v>7.88401198387146</v>
       </c>
       <c r="H8" t="n">
-        <v>7.855488538742065</v>
+        <v>8.353845357894897</v>
       </c>
       <c r="I8" t="n">
-        <v>8.284326076507568</v>
+        <v>7.938089847564697</v>
       </c>
       <c r="J8" t="n">
-        <v>8.284623146057129</v>
+        <v>8.590163946151733</v>
       </c>
       <c r="K8" t="n">
-        <v>8.326849699020386</v>
+        <v>7.372713804244995</v>
       </c>
       <c r="L8" t="n">
-        <v>8.092480087280274</v>
+        <v>7.87971019744873</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>8.586986541748047</v>
+        <v>7.32313346862793</v>
       </c>
       <c r="C9" t="n">
-        <v>8.021615266799927</v>
+        <v>7.781789302825928</v>
       </c>
       <c r="D9" t="n">
-        <v>8.439301252365112</v>
+        <v>7.824447154998779</v>
       </c>
       <c r="E9" t="n">
-        <v>8.419189214706421</v>
+        <v>9.192553758621216</v>
       </c>
       <c r="F9" t="n">
-        <v>8.299496173858643</v>
+        <v>7.944347858428955</v>
       </c>
       <c r="G9" t="n">
-        <v>9.79996919631958</v>
+        <v>7.917701244354248</v>
       </c>
       <c r="H9" t="n">
-        <v>7.935352802276611</v>
+        <v>7.719921350479126</v>
       </c>
       <c r="I9" t="n">
-        <v>7.709205389022827</v>
+        <v>8.189229488372803</v>
       </c>
       <c r="J9" t="n">
-        <v>8.484691858291626</v>
+        <v>7.682560682296753</v>
       </c>
       <c r="K9" t="n">
-        <v>8.053459882736206</v>
+        <v>7.921473026275635</v>
       </c>
       <c r="L9" t="n">
-        <v>8.374926757812499</v>
+        <v>7.949715733528137</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>7.698016166687012</v>
+        <v>7.415798664093018</v>
       </c>
       <c r="C10" t="n">
-        <v>7.784663677215576</v>
+        <v>7.787423133850098</v>
       </c>
       <c r="D10" t="n">
-        <v>7.518819570541382</v>
+        <v>7.058148622512817</v>
       </c>
       <c r="E10" t="n">
-        <v>7.380657434463501</v>
+        <v>7.301583051681519</v>
       </c>
       <c r="F10" t="n">
-        <v>7.426452159881592</v>
+        <v>7.335851669311523</v>
       </c>
       <c r="G10" t="n">
-        <v>7.302550792694092</v>
+        <v>6.912935256958008</v>
       </c>
       <c r="H10" t="n">
-        <v>7.546862840652466</v>
+        <v>7.095400810241699</v>
       </c>
       <c r="I10" t="n">
-        <v>7.14450478553772</v>
+        <v>8.717105388641357</v>
       </c>
       <c r="J10" t="n">
-        <v>7.50878643989563</v>
+        <v>7.765737533569336</v>
       </c>
       <c r="K10" t="n">
-        <v>7.684162378311157</v>
+        <v>7.711087465286255</v>
       </c>
       <c r="L10" t="n">
-        <v>7.499547624588013</v>
+        <v>7.510107159614563</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>7.81228494644165</v>
+        <v>7.212161302566528</v>
       </c>
       <c r="C11" t="n">
-        <v>7.22384786605835</v>
+        <v>6.977260828018188</v>
       </c>
       <c r="D11" t="n">
-        <v>7.10810375213623</v>
+        <v>7.829477310180664</v>
       </c>
       <c r="E11" t="n">
-        <v>7.322885274887085</v>
+        <v>7.039660215377808</v>
       </c>
       <c r="F11" t="n">
-        <v>7.378205537796021</v>
+        <v>8.229791164398193</v>
       </c>
       <c r="G11" t="n">
-        <v>7.983114719390869</v>
+        <v>6.71370792388916</v>
       </c>
       <c r="H11" t="n">
-        <v>7.832049131393433</v>
+        <v>7.441693544387817</v>
       </c>
       <c r="I11" t="n">
-        <v>7.663142919540405</v>
+        <v>7.391802549362183</v>
       </c>
       <c r="J11" t="n">
-        <v>8.323798656463623</v>
+        <v>7.125021934509277</v>
       </c>
       <c r="K11" t="n">
-        <v>7.12574577331543</v>
+        <v>7.152413368225098</v>
       </c>
       <c r="L11" t="n">
-        <v>7.57731785774231</v>
+        <v>7.311299014091492</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>7.565801620483398</v>
+        <v>8.387707233428955</v>
       </c>
       <c r="C12" t="n">
-        <v>7.370442152023315</v>
+        <v>7.863052368164062</v>
       </c>
       <c r="D12" t="n">
-        <v>8.383837223052979</v>
+        <v>8.425077676773071</v>
       </c>
       <c r="E12" t="n">
-        <v>7.859777688980103</v>
+        <v>7.891708135604858</v>
       </c>
       <c r="F12" t="n">
-        <v>7.806378841400146</v>
+        <v>7.561338424682617</v>
       </c>
       <c r="G12" t="n">
-        <v>7.957712173461914</v>
+        <v>7.61426854133606</v>
       </c>
       <c r="H12" t="n">
-        <v>8.211980581283569</v>
+        <v>7.773857593536377</v>
       </c>
       <c r="I12" t="n">
-        <v>8.588243007659912</v>
+        <v>7.9614577293396</v>
       </c>
       <c r="J12" t="n">
-        <v>8.417326927185059</v>
+        <v>7.974775314331055</v>
       </c>
       <c r="K12" t="n">
-        <v>8.234860897064209</v>
+        <v>8.043540477752686</v>
       </c>
       <c r="L12" t="n">
-        <v>8.03963611125946</v>
+        <v>7.949678349494934</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>7.107537031173706</v>
+        <v>7.445964813232422</v>
       </c>
       <c r="C13" t="n">
-        <v>7.813692331314087</v>
+        <v>7.284563064575195</v>
       </c>
       <c r="D13" t="n">
-        <v>7.242215394973755</v>
+        <v>7.379813432693481</v>
       </c>
       <c r="E13" t="n">
-        <v>8.314612865447998</v>
+        <v>8.156013965606689</v>
       </c>
       <c r="F13" t="n">
-        <v>7.371471166610718</v>
+        <v>7.701623201370239</v>
       </c>
       <c r="G13" t="n">
-        <v>9.231188535690308</v>
+        <v>7.419155120849609</v>
       </c>
       <c r="H13" t="n">
-        <v>7.74301815032959</v>
+        <v>7.020135402679443</v>
       </c>
       <c r="I13" t="n">
-        <v>7.924450397491455</v>
+        <v>7.417136430740356</v>
       </c>
       <c r="J13" t="n">
-        <v>7.22745418548584</v>
+        <v>7.356909036636353</v>
       </c>
       <c r="K13" t="n">
-        <v>7.29447865486145</v>
+        <v>7.97562050819397</v>
       </c>
       <c r="L13" t="n">
-        <v>7.727011871337891</v>
+        <v>7.515693497657776</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>9.023566961288452</v>
+        <v>8.671137809753418</v>
       </c>
       <c r="C14" t="n">
-        <v>8.95932412147522</v>
+        <v>8.527543783187866</v>
       </c>
       <c r="D14" t="n">
-        <v>8.369468450546265</v>
+        <v>8.257550477981567</v>
       </c>
       <c r="E14" t="n">
-        <v>8.896886587142944</v>
+        <v>8.550281524658203</v>
       </c>
       <c r="F14" t="n">
-        <v>9.152791023254395</v>
+        <v>7.731940269470215</v>
       </c>
       <c r="G14" t="n">
-        <v>8.419834852218628</v>
+        <v>7.964520215988159</v>
       </c>
       <c r="H14" t="n">
-        <v>8.542676210403442</v>
+        <v>7.69451904296875</v>
       </c>
       <c r="I14" t="n">
-        <v>8.157836437225342</v>
+        <v>7.891981363296509</v>
       </c>
       <c r="J14" t="n">
-        <v>8.585280656814575</v>
+        <v>7.847599506378174</v>
       </c>
       <c r="K14" t="n">
-        <v>8.590240478515625</v>
+        <v>8.925282001495361</v>
       </c>
       <c r="L14" t="n">
-        <v>8.669790577888488</v>
+        <v>8.206235599517822</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>8.253348588943481</v>
+        <v>10.05185699462891</v>
       </c>
       <c r="C15" t="n">
-        <v>9.020255327224731</v>
+        <v>7.601218461990356</v>
       </c>
       <c r="D15" t="n">
-        <v>9.431967496871948</v>
+        <v>7.415733098983765</v>
       </c>
       <c r="E15" t="n">
-        <v>9.244541883468628</v>
+        <v>7.498024463653564</v>
       </c>
       <c r="F15" t="n">
-        <v>9.50758695602417</v>
+        <v>8.16992712020874</v>
       </c>
       <c r="G15" t="n">
-        <v>8.694937705993652</v>
+        <v>7.610230207443237</v>
       </c>
       <c r="H15" t="n">
-        <v>8.89884352684021</v>
+        <v>7.749828815460205</v>
       </c>
       <c r="I15" t="n">
-        <v>8.056974649429321</v>
+        <v>7.516983985900879</v>
       </c>
       <c r="J15" t="n">
-        <v>9.481734752655029</v>
+        <v>8.161309957504272</v>
       </c>
       <c r="K15" t="n">
-        <v>9.554286479949951</v>
+        <v>7.491034746170044</v>
       </c>
       <c r="L15" t="n">
-        <v>9.014447736740113</v>
+        <v>7.926614785194397</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>8.247101545333862</v>
+        <v>7.041693210601807</v>
       </c>
       <c r="C16" t="n">
-        <v>8.343134641647339</v>
+        <v>6.791794300079346</v>
       </c>
       <c r="D16" t="n">
-        <v>8.010079622268677</v>
+        <v>7.898398637771606</v>
       </c>
       <c r="E16" t="n">
-        <v>7.92322039604187</v>
+        <v>6.858531951904297</v>
       </c>
       <c r="F16" t="n">
-        <v>8.075708150863647</v>
+        <v>6.790704250335693</v>
       </c>
       <c r="G16" t="n">
-        <v>8.083556175231934</v>
+        <v>6.790728330612183</v>
       </c>
       <c r="H16" t="n">
-        <v>7.645770788192749</v>
+        <v>6.591706037521362</v>
       </c>
       <c r="I16" t="n">
-        <v>7.663486957550049</v>
+        <v>7.196671724319458</v>
       </c>
       <c r="J16" t="n">
-        <v>8.149344921112061</v>
+        <v>6.826632022857666</v>
       </c>
       <c r="K16" t="n">
-        <v>8.003602266311646</v>
+        <v>7.541957855224609</v>
       </c>
       <c r="L16" t="n">
-        <v>8.014500546455384</v>
+        <v>7.032881832122802</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>8.174900531768799</v>
+        <v>7.484952688217163</v>
       </c>
       <c r="C17" t="n">
-        <v>8.005510330200195</v>
+        <v>8.109873294830322</v>
       </c>
       <c r="D17" t="n">
-        <v>7.641299724578857</v>
+        <v>7.18470311164856</v>
       </c>
       <c r="E17" t="n">
-        <v>8.61194109916687</v>
+        <v>7.505429267883301</v>
       </c>
       <c r="F17" t="n">
-        <v>9.293306827545166</v>
+        <v>8.326356410980225</v>
       </c>
       <c r="G17" t="n">
-        <v>8.423031806945801</v>
+        <v>7.758171081542969</v>
       </c>
       <c r="H17" t="n">
-        <v>8.189765214920044</v>
+        <v>7.499009847640991</v>
       </c>
       <c r="I17" t="n">
-        <v>8.080854177474976</v>
+        <v>8.035420179367065</v>
       </c>
       <c r="J17" t="n">
-        <v>8.694649696350098</v>
+        <v>8.08294939994812</v>
       </c>
       <c r="K17" t="n">
-        <v>9.505674123764038</v>
+        <v>8.137425422668457</v>
       </c>
       <c r="L17" t="n">
-        <v>8.462093353271484</v>
+        <v>7.812429070472717</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>9.110273599624634</v>
+        <v>8.074526786804199</v>
       </c>
       <c r="C18" t="n">
-        <v>9.648963928222656</v>
+        <v>8.435061931610107</v>
       </c>
       <c r="D18" t="n">
-        <v>9.015353441238403</v>
+        <v>7.676539897918701</v>
       </c>
       <c r="E18" t="n">
-        <v>9.317222595214844</v>
+        <v>8.796631813049316</v>
       </c>
       <c r="F18" t="n">
-        <v>9.301693439483643</v>
+        <v>8.323878765106201</v>
       </c>
       <c r="G18" t="n">
-        <v>9.914220333099365</v>
+        <v>8.982742071151733</v>
       </c>
       <c r="H18" t="n">
-        <v>8.922451257705688</v>
+        <v>8.171665668487549</v>
       </c>
       <c r="I18" t="n">
-        <v>8.559878826141357</v>
+        <v>8.11995792388916</v>
       </c>
       <c r="J18" t="n">
-        <v>8.562420606613159</v>
+        <v>8.369710683822632</v>
       </c>
       <c r="K18" t="n">
-        <v>9.431888818740845</v>
+        <v>8.809105634689331</v>
       </c>
       <c r="L18" t="n">
-        <v>9.17843668460846</v>
+        <v>8.375982117652892</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>7.004103183746338</v>
+        <v>7.810715198516846</v>
       </c>
       <c r="C19" t="n">
-        <v>7.358799457550049</v>
+        <v>6.871635913848877</v>
       </c>
       <c r="D19" t="n">
-        <v>7.607096672058105</v>
+        <v>7.609292507171631</v>
       </c>
       <c r="E19" t="n">
-        <v>6.974035739898682</v>
+        <v>7.014843225479126</v>
       </c>
       <c r="F19" t="n">
-        <v>7.053624868392944</v>
+        <v>6.856192350387573</v>
       </c>
       <c r="G19" t="n">
-        <v>7.006328105926514</v>
+        <v>6.781362771987915</v>
       </c>
       <c r="H19" t="n">
-        <v>7.011122941970825</v>
+        <v>6.75201678276062</v>
       </c>
       <c r="I19" t="n">
-        <v>7.564537525177002</v>
+        <v>6.65469217300415</v>
       </c>
       <c r="J19" t="n">
-        <v>7.132413864135742</v>
+        <v>6.395383834838867</v>
       </c>
       <c r="K19" t="n">
-        <v>7.697388887405396</v>
+        <v>8.912319183349609</v>
       </c>
       <c r="L19" t="n">
-        <v>7.24094512462616</v>
+        <v>7.165845394134521</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>7.808211803436279</v>
+        <v>6.987825870513916</v>
       </c>
       <c r="C20" t="n">
-        <v>7.929267644882202</v>
+        <v>6.803391456604004</v>
       </c>
       <c r="D20" t="n">
-        <v>8.496753931045532</v>
+        <v>7.784247398376465</v>
       </c>
       <c r="E20" t="n">
-        <v>8.114466905593872</v>
+        <v>8.595685482025146</v>
       </c>
       <c r="F20" t="n">
-        <v>7.468189716339111</v>
+        <v>6.487650632858276</v>
       </c>
       <c r="G20" t="n">
-        <v>9.010109901428223</v>
+        <v>6.941454410552979</v>
       </c>
       <c r="H20" t="n">
-        <v>7.888774394989014</v>
+        <v>7.476089477539062</v>
       </c>
       <c r="I20" t="n">
-        <v>7.817473173141479</v>
+        <v>7.713518857955933</v>
       </c>
       <c r="J20" t="n">
-        <v>7.924684047698975</v>
+        <v>7.209251880645752</v>
       </c>
       <c r="K20" t="n">
-        <v>8.457342863082886</v>
+        <v>7.785260438919067</v>
       </c>
       <c r="L20" t="n">
-        <v>8.091527438163757</v>
+        <v>7.37843759059906</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>8.721894264221191</v>
+        <v>7.210348129272461</v>
       </c>
       <c r="C21" t="n">
-        <v>7.495435476303101</v>
+        <v>8.006169080734253</v>
       </c>
       <c r="D21" t="n">
-        <v>8.418930053710938</v>
+        <v>8.497421979904175</v>
       </c>
       <c r="E21" t="n">
-        <v>7.922133207321167</v>
+        <v>7.266597270965576</v>
       </c>
       <c r="F21" t="n">
-        <v>8.238107681274414</v>
+        <v>8.266502380371094</v>
       </c>
       <c r="G21" t="n">
-        <v>8.487018585205078</v>
+        <v>8.500382900238037</v>
       </c>
       <c r="H21" t="n">
-        <v>7.821336030960083</v>
+        <v>7.339401960372925</v>
       </c>
       <c r="I21" t="n">
-        <v>8.474625587463379</v>
+        <v>7.649138450622559</v>
       </c>
       <c r="J21" t="n">
-        <v>8.54097318649292</v>
+        <v>8.068531513214111</v>
       </c>
       <c r="K21" t="n">
-        <v>8.38427734375</v>
+        <v>7.476553440093994</v>
       </c>
       <c r="L21" t="n">
-        <v>8.250473141670227</v>
+        <v>7.828104710578918</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>8.030369520187378</v>
+        <v>6.467217683792114</v>
       </c>
       <c r="C22" t="n">
-        <v>7.989698886871338</v>
+        <v>6.94342565536499</v>
       </c>
       <c r="D22" t="n">
-        <v>7.862090587615967</v>
+        <v>6.764893054962158</v>
       </c>
       <c r="E22" t="n">
-        <v>8.920313119888306</v>
+        <v>6.617782115936279</v>
       </c>
       <c r="F22" t="n">
-        <v>8.97200345993042</v>
+        <v>6.463760375976562</v>
       </c>
       <c r="G22" t="n">
-        <v>7.101989984512329</v>
+        <v>6.858198642730713</v>
       </c>
       <c r="H22" t="n">
-        <v>7.869970083236694</v>
+        <v>6.595858335494995</v>
       </c>
       <c r="I22" t="n">
-        <v>8.811396837234497</v>
+        <v>6.806308269500732</v>
       </c>
       <c r="J22" t="n">
-        <v>8.458799123764038</v>
+        <v>8.507387399673462</v>
       </c>
       <c r="K22" t="n">
-        <v>7.714568853378296</v>
+        <v>7.243149280548096</v>
       </c>
       <c r="L22" t="n">
-        <v>8.173120045661927</v>
+        <v>6.92679808139801</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>10.67199087142944</v>
+        <v>8.887877464294434</v>
       </c>
       <c r="C23" t="n">
-        <v>8.742567300796509</v>
+        <v>8.805119037628174</v>
       </c>
       <c r="D23" t="n">
-        <v>16.62103343009949</v>
+        <v>10.22638988494873</v>
       </c>
       <c r="E23" t="n">
-        <v>10.69143509864807</v>
+        <v>8.409149408340454</v>
       </c>
       <c r="F23" t="n">
-        <v>9.304499864578247</v>
+        <v>9.053478956222534</v>
       </c>
       <c r="G23" t="n">
-        <v>9.286151647567749</v>
+        <v>8.898353815078735</v>
       </c>
       <c r="H23" t="n">
-        <v>8.946084499359131</v>
+        <v>8.181747198104858</v>
       </c>
       <c r="I23" t="n">
-        <v>8.93704080581665</v>
+        <v>8.019144058227539</v>
       </c>
       <c r="J23" t="n">
-        <v>9.663532257080078</v>
+        <v>8.051072597503662</v>
       </c>
       <c r="K23" t="n">
-        <v>8.949010133743286</v>
+        <v>8.491032123565674</v>
       </c>
       <c r="L23" t="n">
-        <v>10.18133459091186</v>
+        <v>8.70233645439148</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>7.759356021881104</v>
+        <v>6.686130523681641</v>
       </c>
       <c r="C24" t="n">
-        <v>7.336790561676025</v>
+        <v>7.9359130859375</v>
       </c>
       <c r="D24" t="n">
-        <v>7.520982027053833</v>
+        <v>6.967380285263062</v>
       </c>
       <c r="E24" t="n">
-        <v>7.996800661087036</v>
+        <v>7.396779537200928</v>
       </c>
       <c r="F24" t="n">
-        <v>6.789374589920044</v>
+        <v>8.289811134338379</v>
       </c>
       <c r="G24" t="n">
-        <v>7.866241455078125</v>
+        <v>6.507917404174805</v>
       </c>
       <c r="H24" t="n">
-        <v>7.273777961730957</v>
+        <v>7.047084093093872</v>
       </c>
       <c r="I24" t="n">
-        <v>7.841249465942383</v>
+        <v>7.56525707244873</v>
       </c>
       <c r="J24" t="n">
-        <v>8.020963907241821</v>
+        <v>7.698951959609985</v>
       </c>
       <c r="K24" t="n">
-        <v>8.559706926345825</v>
+        <v>7.061719655990601</v>
       </c>
       <c r="L24" t="n">
-        <v>7.696524357795715</v>
+        <v>7.315694475173951</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>9.316470384597778</v>
+        <v>10.63346195220947</v>
       </c>
       <c r="C25" t="n">
-        <v>9.281481742858887</v>
+        <v>9.03649115562439</v>
       </c>
       <c r="D25" t="n">
-        <v>9.410601615905762</v>
+        <v>9.02357816696167</v>
       </c>
       <c r="E25" t="n">
-        <v>8.931970357894897</v>
+        <v>8.01017165184021</v>
       </c>
       <c r="F25" t="n">
-        <v>9.781234502792358</v>
+        <v>8.030191421508789</v>
       </c>
       <c r="G25" t="n">
-        <v>11.47220420837402</v>
+        <v>8.477477312088013</v>
       </c>
       <c r="H25" t="n">
-        <v>8.99194073677063</v>
+        <v>8.858026266098022</v>
       </c>
       <c r="I25" t="n">
-        <v>9.168800592422485</v>
+        <v>9.20209527015686</v>
       </c>
       <c r="J25" t="n">
-        <v>8.577013254165649</v>
+        <v>9.501794576644897</v>
       </c>
       <c r="K25" t="n">
-        <v>9.676653146743774</v>
+        <v>9.150720357894897</v>
       </c>
       <c r="L25" t="n">
-        <v>9.460837054252625</v>
+        <v>8.992400813102723</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>8.436086654663086</v>
+        <v>7.507989645004272</v>
       </c>
       <c r="C26" t="n">
-        <v>10.77195858955383</v>
+        <v>7.771825313568115</v>
       </c>
       <c r="D26" t="n">
-        <v>8.705939531326294</v>
+        <v>7.717488288879395</v>
       </c>
       <c r="E26" t="n">
-        <v>10.34558463096619</v>
+        <v>7.310773849487305</v>
       </c>
       <c r="F26" t="n">
-        <v>8.471889019012451</v>
+        <v>9.246473550796509</v>
       </c>
       <c r="G26" t="n">
-        <v>10.15207290649414</v>
+        <v>8.7821204662323</v>
       </c>
       <c r="H26" t="n">
-        <v>9.035944938659668</v>
+        <v>8.520834684371948</v>
       </c>
       <c r="I26" t="n">
-        <v>7.56802225112915</v>
+        <v>7.718817949295044</v>
       </c>
       <c r="J26" t="n">
-        <v>8.391259670257568</v>
+        <v>7.876927375793457</v>
       </c>
       <c r="K26" t="n">
-        <v>8.207547187805176</v>
+        <v>7.692952632904053</v>
       </c>
       <c r="L26" t="n">
-        <v>9.008630537986756</v>
+        <v>8.014620375633239</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>10.45675563812256</v>
+        <v>9.495360374450684</v>
       </c>
       <c r="C27" t="n">
-        <v>9.119479894638062</v>
+        <v>8.521783590316772</v>
       </c>
       <c r="D27" t="n">
-        <v>9.032995939254761</v>
+        <v>8.199145793914795</v>
       </c>
       <c r="E27" t="n">
-        <v>9.369103908538818</v>
+        <v>9.055941343307495</v>
       </c>
       <c r="F27" t="n">
-        <v>9.4135422706604</v>
+        <v>8.151741027832031</v>
       </c>
       <c r="G27" t="n">
-        <v>9.648481607437134</v>
+        <v>7.943805694580078</v>
       </c>
       <c r="H27" t="n">
-        <v>9.274607181549072</v>
+        <v>8.84250020980835</v>
       </c>
       <c r="I27" t="n">
-        <v>9.140236377716064</v>
+        <v>9.369645118713379</v>
       </c>
       <c r="J27" t="n">
-        <v>9.356210231781006</v>
+        <v>8.442012786865234</v>
       </c>
       <c r="K27" t="n">
-        <v>9.33051061630249</v>
+        <v>8.677900791168213</v>
       </c>
       <c r="L27" t="n">
-        <v>9.414192366600037</v>
+        <v>8.669983673095704</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.864982128143311</v>
+        <v>7.469476938247681</v>
       </c>
       <c r="C28" t="n">
-        <v>7.858200311660767</v>
+        <v>9.157576084136963</v>
       </c>
       <c r="D28" t="n">
-        <v>7.861139535903931</v>
+        <v>8.200247287750244</v>
       </c>
       <c r="E28" t="n">
-        <v>7.655072689056396</v>
+        <v>8.687625646591187</v>
       </c>
       <c r="F28" t="n">
-        <v>7.776899337768555</v>
+        <v>7.412163972854614</v>
       </c>
       <c r="G28" t="n">
-        <v>7.90143084526062</v>
+        <v>6.849603652954102</v>
       </c>
       <c r="H28" t="n">
-        <v>7.685033559799194</v>
+        <v>7.462007761001587</v>
       </c>
       <c r="I28" t="n">
-        <v>7.868157625198364</v>
+        <v>7.882645130157471</v>
       </c>
       <c r="J28" t="n">
-        <v>7.924466848373413</v>
+        <v>7.686988115310669</v>
       </c>
       <c r="K28" t="n">
-        <v>8.194190979003906</v>
+        <v>8.114911556243896</v>
       </c>
       <c r="L28" t="n">
-        <v>7.858957386016845</v>
+        <v>7.892324614524841</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>7.551428318023682</v>
+        <v>7.361797332763672</v>
       </c>
       <c r="C29" t="n">
-        <v>7.93462347984314</v>
+        <v>8.337347984313965</v>
       </c>
       <c r="D29" t="n">
-        <v>7.894095420837402</v>
+        <v>8.206217765808105</v>
       </c>
       <c r="E29" t="n">
-        <v>7.778563261032104</v>
+        <v>7.465513944625854</v>
       </c>
       <c r="F29" t="n">
-        <v>8.993288993835449</v>
+        <v>7.753757476806641</v>
       </c>
       <c r="G29" t="n">
-        <v>7.504100799560547</v>
+        <v>7.695904970169067</v>
       </c>
       <c r="H29" t="n">
-        <v>8.312382936477661</v>
+        <v>7.619603872299194</v>
       </c>
       <c r="I29" t="n">
-        <v>7.551503658294678</v>
+        <v>7.147310018539429</v>
       </c>
       <c r="J29" t="n">
-        <v>8.308826446533203</v>
+        <v>7.381207466125488</v>
       </c>
       <c r="K29" t="n">
-        <v>7.718629360198975</v>
+        <v>8.334352970123291</v>
       </c>
       <c r="L29" t="n">
-        <v>7.954744267463684</v>
+        <v>7.730301380157471</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>7.995174884796143</v>
+        <v>7.785186529159546</v>
       </c>
       <c r="C30" t="n">
-        <v>9.000733613967896</v>
+        <v>7.493416309356689</v>
       </c>
       <c r="D30" t="n">
-        <v>8.559215545654297</v>
+        <v>8.74427604675293</v>
       </c>
       <c r="E30" t="n">
-        <v>7.491554975509644</v>
+        <v>7.059023857116699</v>
       </c>
       <c r="F30" t="n">
-        <v>7.952096700668335</v>
+        <v>7.869486331939697</v>
       </c>
       <c r="G30" t="n">
-        <v>8.080007076263428</v>
+        <v>8.416693210601807</v>
       </c>
       <c r="H30" t="n">
-        <v>7.779257535934448</v>
+        <v>8.607651948928833</v>
       </c>
       <c r="I30" t="n">
-        <v>8.392606496810913</v>
+        <v>7.93088173866272</v>
       </c>
       <c r="J30" t="n">
-        <v>7.952088594436646</v>
+        <v>6.971380233764648</v>
       </c>
       <c r="K30" t="n">
-        <v>7.979992866516113</v>
+        <v>7.259618043899536</v>
       </c>
       <c r="L30" t="n">
-        <v>8.118272829055787</v>
+        <v>7.813761425018311</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>7.732869148254395</v>
+        <v>8.585206508636475</v>
       </c>
       <c r="C31" t="n">
-        <v>7.472650051116943</v>
+        <v>8.034646511077881</v>
       </c>
       <c r="D31" t="n">
-        <v>7.990289211273193</v>
+        <v>6.989861249923706</v>
       </c>
       <c r="E31" t="n">
-        <v>8.066468715667725</v>
+        <v>6.997186660766602</v>
       </c>
       <c r="F31" t="n">
-        <v>7.429091453552246</v>
+        <v>7.398186683654785</v>
       </c>
       <c r="G31" t="n">
-        <v>7.669099807739258</v>
+        <v>7.217380285263062</v>
       </c>
       <c r="H31" t="n">
-        <v>8.400890111923218</v>
+        <v>7.169388055801392</v>
       </c>
       <c r="I31" t="n">
-        <v>8.526577949523926</v>
+        <v>7.019788503646851</v>
       </c>
       <c r="J31" t="n">
-        <v>8.209415435791016</v>
+        <v>7.029745578765869</v>
       </c>
       <c r="K31" t="n">
-        <v>8.648233890533447</v>
+        <v>6.896597862243652</v>
       </c>
       <c r="L31" t="n">
-        <v>8.014558577537537</v>
+        <v>7.333798789978028</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>9.654494524002075</v>
+        <v>8.325873136520386</v>
       </c>
       <c r="C32" t="n">
-        <v>9.461887836456299</v>
+        <v>7.80970573425293</v>
       </c>
       <c r="D32" t="n">
-        <v>8.597552537918091</v>
+        <v>8.091886281967163</v>
       </c>
       <c r="E32" t="n">
-        <v>9.627070188522339</v>
+        <v>7.871468782424927</v>
       </c>
       <c r="F32" t="n">
-        <v>12.17956781387329</v>
+        <v>8.724341869354248</v>
       </c>
       <c r="G32" t="n">
-        <v>10.79804444313049</v>
+        <v>8.071438789367676</v>
       </c>
       <c r="H32" t="n">
-        <v>9.073408842086792</v>
+        <v>8.043015241622925</v>
       </c>
       <c r="I32" t="n">
-        <v>8.563748359680176</v>
+        <v>8.30937671661377</v>
       </c>
       <c r="J32" t="n">
-        <v>8.386651992797852</v>
+        <v>8.175684452056885</v>
       </c>
       <c r="K32" t="n">
-        <v>8.343276500701904</v>
+        <v>8.303342342376709</v>
       </c>
       <c r="L32" t="n">
-        <v>9.46857030391693</v>
+        <v>8.172613334655761</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>7.369271278381348</v>
+        <v>7.433086156845093</v>
       </c>
       <c r="C33" t="n">
-        <v>7.576732873916626</v>
+        <v>6.857074737548828</v>
       </c>
       <c r="D33" t="n">
-        <v>8.149846076965332</v>
+        <v>6.769275426864624</v>
       </c>
       <c r="E33" t="n">
-        <v>7.894405841827393</v>
+        <v>7.129335880279541</v>
       </c>
       <c r="F33" t="n">
-        <v>9.312356472015381</v>
+        <v>7.521362066268921</v>
       </c>
       <c r="G33" t="n">
-        <v>7.505445957183838</v>
+        <v>7.087462425231934</v>
       </c>
       <c r="H33" t="n">
-        <v>8.521833181381226</v>
+        <v>6.801708698272705</v>
       </c>
       <c r="I33" t="n">
-        <v>7.556797742843628</v>
+        <v>6.978250741958618</v>
       </c>
       <c r="J33" t="n">
-        <v>8.203168153762817</v>
+        <v>7.6081383228302</v>
       </c>
       <c r="K33" t="n">
-        <v>7.656537532806396</v>
+        <v>7.781903505325317</v>
       </c>
       <c r="L33" t="n">
-        <v>7.974639511108398</v>
+        <v>7.196759796142578</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>7.473488330841064</v>
+        <v>8.038527965545654</v>
       </c>
       <c r="C34" t="n">
-        <v>8.126856327056885</v>
+        <v>8.0016028881073</v>
       </c>
       <c r="D34" t="n">
-        <v>8.637052297592163</v>
+        <v>8.297361135482788</v>
       </c>
       <c r="E34" t="n">
-        <v>7.551276206970215</v>
+        <v>7.845006942749023</v>
       </c>
       <c r="F34" t="n">
-        <v>8.234562397003174</v>
+        <v>8.398625373840332</v>
       </c>
       <c r="G34" t="n">
-        <v>8.305891275405884</v>
+        <v>8.173740148544312</v>
       </c>
       <c r="H34" t="n">
-        <v>7.482470989227295</v>
+        <v>8.025176048278809</v>
       </c>
       <c r="I34" t="n">
-        <v>8.053529977798462</v>
+        <v>8.138358116149902</v>
       </c>
       <c r="J34" t="n">
-        <v>7.951784372329712</v>
+        <v>7.390316486358643</v>
       </c>
       <c r="K34" t="n">
-        <v>7.921344995498657</v>
+        <v>7.831647396087646</v>
       </c>
       <c r="L34" t="n">
-        <v>7.973825716972351</v>
+        <v>8.01403625011444</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.523482084274292</v>
+        <v>7.18482232093811</v>
       </c>
       <c r="C35" t="n">
-        <v>7.424152851104736</v>
+        <v>7.114994525909424</v>
       </c>
       <c r="D35" t="n">
-        <v>8.60413122177124</v>
+        <v>7.043696403503418</v>
       </c>
       <c r="E35" t="n">
-        <v>7.342093229293823</v>
+        <v>7.003800868988037</v>
       </c>
       <c r="F35" t="n">
-        <v>7.77181339263916</v>
+        <v>7.223231554031372</v>
       </c>
       <c r="G35" t="n">
-        <v>7.618208646774292</v>
+        <v>7.605909109115601</v>
       </c>
       <c r="H35" t="n">
-        <v>8.094980955123901</v>
+        <v>7.39616847038269</v>
       </c>
       <c r="I35" t="n">
-        <v>7.502004146575928</v>
+        <v>7.044049739837646</v>
       </c>
       <c r="J35" t="n">
-        <v>7.518958330154419</v>
+        <v>7.435561180114746</v>
       </c>
       <c r="K35" t="n">
-        <v>7.9603111743927</v>
+        <v>7.288423538208008</v>
       </c>
       <c r="L35" t="n">
-        <v>7.736013603210449</v>
+        <v>7.234065771102905</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>7.747377157211304</v>
+        <v>8.67640495300293</v>
       </c>
       <c r="C36" t="n">
-        <v>7.88108229637146</v>
+        <v>8.473921060562134</v>
       </c>
       <c r="D36" t="n">
-        <v>7.667103052139282</v>
+        <v>7.577197551727295</v>
       </c>
       <c r="E36" t="n">
-        <v>10.83274006843567</v>
+        <v>7.685956716537476</v>
       </c>
       <c r="F36" t="n">
-        <v>8.480716228485107</v>
+        <v>9.11130166053772</v>
       </c>
       <c r="G36" t="n">
-        <v>7.995800495147705</v>
+        <v>7.511368274688721</v>
       </c>
       <c r="H36" t="n">
-        <v>8.86530613899231</v>
+        <v>7.446048498153687</v>
       </c>
       <c r="I36" t="n">
-        <v>8.375401735305786</v>
+        <v>7.66648268699646</v>
       </c>
       <c r="J36" t="n">
-        <v>8.237210750579834</v>
+        <v>7.428578615188599</v>
       </c>
       <c r="K36" t="n">
-        <v>8.167139530181885</v>
+        <v>7.500909805297852</v>
       </c>
       <c r="L36" t="n">
-        <v>8.424987745285033</v>
+        <v>7.907816982269287</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>7.37911319732666</v>
+        <v>6.612185478210449</v>
       </c>
       <c r="C37" t="n">
-        <v>7.513845920562744</v>
+        <v>6.424182415008545</v>
       </c>
       <c r="D37" t="n">
-        <v>8.128503084182739</v>
+        <v>6.630119562149048</v>
       </c>
       <c r="E37" t="n">
-        <v>7.200877666473389</v>
+        <v>7.009147882461548</v>
       </c>
       <c r="F37" t="n">
-        <v>7.451600551605225</v>
+        <v>6.447613477706909</v>
       </c>
       <c r="G37" t="n">
-        <v>10.02403092384338</v>
+        <v>6.815636396408081</v>
       </c>
       <c r="H37" t="n">
-        <v>7.423731565475464</v>
+        <v>6.546825408935547</v>
       </c>
       <c r="I37" t="n">
-        <v>6.929069757461548</v>
+        <v>6.634110927581787</v>
       </c>
       <c r="J37" t="n">
-        <v>7.001342535018921</v>
+        <v>6.513983249664307</v>
       </c>
       <c r="K37" t="n">
-        <v>7.102066040039062</v>
+        <v>6.576259136199951</v>
       </c>
       <c r="L37" t="n">
-        <v>7.615418124198913</v>
+        <v>6.621006393432618</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>7.70646333694458</v>
+        <v>6.808651208877563</v>
       </c>
       <c r="C38" t="n">
-        <v>7.172407388687134</v>
+        <v>7.150178909301758</v>
       </c>
       <c r="D38" t="n">
-        <v>6.84523606300354</v>
+        <v>8.809557914733887</v>
       </c>
       <c r="E38" t="n">
-        <v>7.637167453765869</v>
+        <v>6.777734994888306</v>
       </c>
       <c r="F38" t="n">
-        <v>6.985847473144531</v>
+        <v>6.799709558486938</v>
       </c>
       <c r="G38" t="n">
-        <v>7.02779221534729</v>
+        <v>6.80863618850708</v>
       </c>
       <c r="H38" t="n">
-        <v>7.229232311248779</v>
+        <v>6.707436323165894</v>
       </c>
       <c r="I38" t="n">
-        <v>7.569324016571045</v>
+        <v>7.08000636100769</v>
       </c>
       <c r="J38" t="n">
-        <v>8.406401634216309</v>
+        <v>7.665021657943726</v>
       </c>
       <c r="K38" t="n">
-        <v>7.189224720001221</v>
+        <v>7.016117572784424</v>
       </c>
       <c r="L38" t="n">
-        <v>7.37690966129303</v>
+        <v>7.162305068969727</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>8.456515550613403</v>
+        <v>7.08844780921936</v>
       </c>
       <c r="C39" t="n">
-        <v>7.655533790588379</v>
+        <v>7.965224981307983</v>
       </c>
       <c r="D39" t="n">
-        <v>7.518397331237793</v>
+        <v>7.311889171600342</v>
       </c>
       <c r="E39" t="n">
-        <v>7.726877212524414</v>
+        <v>7.17473840713501</v>
       </c>
       <c r="F39" t="n">
-        <v>7.403170824050903</v>
+        <v>7.908851146697998</v>
       </c>
       <c r="G39" t="n">
-        <v>7.506407022476196</v>
+        <v>8.716794729232788</v>
       </c>
       <c r="H39" t="n">
-        <v>7.861566781997681</v>
+        <v>8.131344079971313</v>
       </c>
       <c r="I39" t="n">
-        <v>7.395725011825562</v>
+        <v>7.213657140731812</v>
       </c>
       <c r="J39" t="n">
-        <v>7.606620788574219</v>
+        <v>7.582202672958374</v>
       </c>
       <c r="K39" t="n">
-        <v>7.820151805877686</v>
+        <v>7.865490674972534</v>
       </c>
       <c r="L39" t="n">
-        <v>7.695096611976624</v>
+        <v>7.695864081382751</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>7.014167547225952</v>
+        <v>6.772803068161011</v>
       </c>
       <c r="C40" t="n">
-        <v>8.328319787979126</v>
+        <v>6.999788999557495</v>
       </c>
       <c r="D40" t="n">
-        <v>7.216123342514038</v>
+        <v>7.01373815536499</v>
       </c>
       <c r="E40" t="n">
-        <v>7.354835987091064</v>
+        <v>7.414718389511108</v>
       </c>
       <c r="F40" t="n">
-        <v>7.290003299713135</v>
+        <v>6.901774406433105</v>
       </c>
       <c r="G40" t="n">
-        <v>7.299395084381104</v>
+        <v>7.062016010284424</v>
       </c>
       <c r="H40" t="n">
-        <v>7.44953179359436</v>
+        <v>7.521350145339966</v>
       </c>
       <c r="I40" t="n">
-        <v>7.234614372253418</v>
+        <v>7.38653302192688</v>
       </c>
       <c r="J40" t="n">
-        <v>7.112424373626709</v>
+        <v>7.064513444900513</v>
       </c>
       <c r="K40" t="n">
-        <v>7.530318260192871</v>
+        <v>7.235586166381836</v>
       </c>
       <c r="L40" t="n">
-        <v>7.382973384857178</v>
+        <v>7.137282180786133</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>7.480473041534424</v>
+        <v>7.30590295791626</v>
       </c>
       <c r="C41" t="n">
-        <v>7.087970972061157</v>
+        <v>7.08000111579895</v>
       </c>
       <c r="D41" t="n">
-        <v>8.079097509384155</v>
+        <v>7.219598531723022</v>
       </c>
       <c r="E41" t="n">
-        <v>7.2226243019104</v>
+        <v>6.746850252151489</v>
       </c>
       <c r="F41" t="n">
-        <v>7.488153219223022</v>
+        <v>6.944812297821045</v>
       </c>
       <c r="G41" t="n">
-        <v>7.854633569717407</v>
+        <v>6.729361772537231</v>
       </c>
       <c r="H41" t="n">
-        <v>7.389770269393921</v>
+        <v>7.026117563247681</v>
       </c>
       <c r="I41" t="n">
-        <v>6.982874155044556</v>
+        <v>6.869038343429565</v>
       </c>
       <c r="J41" t="n">
-        <v>7.066631555557251</v>
+        <v>6.71241021156311</v>
       </c>
       <c r="K41" t="n">
-        <v>7.444666624069214</v>
+        <v>6.976730585098267</v>
       </c>
       <c r="L41" t="n">
-        <v>7.40968952178955</v>
+        <v>6.961082363128662</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>7.932862520217896</v>
+        <v>8.471407175064087</v>
       </c>
       <c r="C42" t="n">
-        <v>8.346875905990601</v>
+        <v>7.349792957305908</v>
       </c>
       <c r="D42" t="n">
-        <v>7.782789707183838</v>
+        <v>7.938782930374146</v>
       </c>
       <c r="E42" t="n">
-        <v>8.051120758056641</v>
+        <v>7.415134191513062</v>
       </c>
       <c r="F42" t="n">
-        <v>7.619238138198853</v>
+        <v>7.504854440689087</v>
       </c>
       <c r="G42" t="n">
-        <v>7.910958528518677</v>
+        <v>8.762671709060669</v>
       </c>
       <c r="H42" t="n">
-        <v>7.257665157318115</v>
+        <v>7.425087451934814</v>
       </c>
       <c r="I42" t="n">
-        <v>7.89148998260498</v>
+        <v>7.439050912857056</v>
       </c>
       <c r="J42" t="n">
-        <v>6.934470415115356</v>
+        <v>8.131844282150269</v>
       </c>
       <c r="K42" t="n">
-        <v>7.681539058685303</v>
+        <v>7.234570503234863</v>
       </c>
       <c r="L42" t="n">
-        <v>7.740901017189026</v>
+        <v>7.767319655418396</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>7.459289789199829</v>
+        <v>6.90241813659668</v>
       </c>
       <c r="C43" t="n">
-        <v>7.89631462097168</v>
+        <v>7.190682888031006</v>
       </c>
       <c r="D43" t="n">
-        <v>7.199178695678711</v>
+        <v>8.085956573486328</v>
       </c>
       <c r="E43" t="n">
-        <v>7.768263578414917</v>
+        <v>7.07099723815918</v>
       </c>
       <c r="F43" t="n">
-        <v>7.542331695556641</v>
+        <v>7.093426942825317</v>
       </c>
       <c r="G43" t="n">
-        <v>7.261026382446289</v>
+        <v>8.030578851699829</v>
       </c>
       <c r="H43" t="n">
-        <v>8.392178773880005</v>
+        <v>7.528349161148071</v>
       </c>
       <c r="I43" t="n">
-        <v>9.124315977096558</v>
+        <v>7.884411573410034</v>
       </c>
       <c r="J43" t="n">
-        <v>7.504467725753784</v>
+        <v>7.616674661636353</v>
       </c>
       <c r="K43" t="n">
-        <v>7.871479272842407</v>
+        <v>7.170752048492432</v>
       </c>
       <c r="L43" t="n">
-        <v>7.801884651184082</v>
+        <v>7.457424807548523</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>6.272081613540649</v>
+        <v>6.614156246185303</v>
       </c>
       <c r="C44" t="n">
-        <v>6.676533460617065</v>
+        <v>6.414669036865234</v>
       </c>
       <c r="D44" t="n">
-        <v>6.36129355430603</v>
+        <v>6.388220310211182</v>
       </c>
       <c r="E44" t="n">
-        <v>7.129887104034424</v>
+        <v>6.501976013183594</v>
       </c>
       <c r="F44" t="n">
-        <v>6.227161407470703</v>
+        <v>6.448579549789429</v>
       </c>
       <c r="G44" t="n">
-        <v>6.738393545150757</v>
+        <v>6.417696475982666</v>
       </c>
       <c r="H44" t="n">
-        <v>6.464548110961914</v>
+        <v>6.238641500473022</v>
       </c>
       <c r="I44" t="n">
-        <v>6.985240936279297</v>
+        <v>6.567775726318359</v>
       </c>
       <c r="J44" t="n">
-        <v>7.527940034866333</v>
+        <v>6.270519018173218</v>
       </c>
       <c r="K44" t="n">
-        <v>6.632121562957764</v>
+        <v>6.294499635696411</v>
       </c>
       <c r="L44" t="n">
-        <v>6.701520133018493</v>
+        <v>6.415673351287841</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>10.67885756492615</v>
+        <v>8.620043754577637</v>
       </c>
       <c r="C45" t="n">
-        <v>8.527815341949463</v>
+        <v>7.774693250656128</v>
       </c>
       <c r="D45" t="n">
-        <v>8.759738445281982</v>
+        <v>7.891417741775513</v>
       </c>
       <c r="E45" t="n">
-        <v>8.243102550506592</v>
+        <v>8.312353849411011</v>
       </c>
       <c r="F45" t="n">
-        <v>8.621080636978149</v>
+        <v>8.179202318191528</v>
       </c>
       <c r="G45" t="n">
-        <v>9.008062362670898</v>
+        <v>8.78663158416748</v>
       </c>
       <c r="H45" t="n">
-        <v>7.790182590484619</v>
+        <v>7.822072267532349</v>
       </c>
       <c r="I45" t="n">
-        <v>7.83305835723877</v>
+        <v>8.83452320098877</v>
       </c>
       <c r="J45" t="n">
-        <v>8.100907325744629</v>
+        <v>7.937833309173584</v>
       </c>
       <c r="K45" t="n">
-        <v>8.181711435317993</v>
+        <v>8.01509952545166</v>
       </c>
       <c r="L45" t="n">
-        <v>8.574451661109924</v>
+        <v>8.217387080192566</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>7.118373870849609</v>
+        <v>7.264547348022461</v>
       </c>
       <c r="C46" t="n">
-        <v>8.933816194534302</v>
+        <v>7.100465774536133</v>
       </c>
       <c r="D46" t="n">
-        <v>7.053584337234497</v>
+        <v>6.67798924446106</v>
       </c>
       <c r="E46" t="n">
-        <v>7.172231674194336</v>
+        <v>6.885960578918457</v>
       </c>
       <c r="F46" t="n">
-        <v>9.092375516891479</v>
+        <v>6.746320724487305</v>
       </c>
       <c r="G46" t="n">
-        <v>7.367252111434937</v>
+        <v>6.620196342468262</v>
       </c>
       <c r="H46" t="n">
-        <v>7.063019037246704</v>
+        <v>6.884458303451538</v>
       </c>
       <c r="I46" t="n">
-        <v>7.587706565856934</v>
+        <v>6.845104455947876</v>
       </c>
       <c r="J46" t="n">
-        <v>6.758995294570923</v>
+        <v>6.80815601348877</v>
       </c>
       <c r="K46" t="n">
-        <v>8.170201539993286</v>
+        <v>6.929386377334595</v>
       </c>
       <c r="L46" t="n">
-        <v>7.631755614280701</v>
+        <v>6.876258516311646</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.20521354675293</v>
+        <v>7.978240251541138</v>
       </c>
       <c r="C47" t="n">
-        <v>7.979214429855347</v>
+        <v>7.876409292221069</v>
       </c>
       <c r="D47" t="n">
-        <v>7.946770668029785</v>
+        <v>8.156745433807373</v>
       </c>
       <c r="E47" t="n">
-        <v>8.823547601699829</v>
+        <v>8.823609828948975</v>
       </c>
       <c r="F47" t="n">
-        <v>8.077486753463745</v>
+        <v>7.795763731002808</v>
       </c>
       <c r="G47" t="n">
-        <v>8.425572633743286</v>
+        <v>9.540763139724731</v>
       </c>
       <c r="H47" t="n">
-        <v>7.778198480606079</v>
+        <v>10.0643367767334</v>
       </c>
       <c r="I47" t="n">
-        <v>9.196677446365356</v>
+        <v>7.952829360961914</v>
       </c>
       <c r="J47" t="n">
-        <v>7.965224266052246</v>
+        <v>8.125365495681763</v>
       </c>
       <c r="K47" t="n">
-        <v>8.103874683380127</v>
+        <v>8.924336910247803</v>
       </c>
       <c r="L47" t="n">
-        <v>8.250178050994872</v>
+        <v>8.523840022087096</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>6.822629451751709</v>
+        <v>7.835790157318115</v>
       </c>
       <c r="C48" t="n">
-        <v>6.890035629272461</v>
+        <v>6.07502293586731</v>
       </c>
       <c r="D48" t="n">
-        <v>6.858062505722046</v>
+        <v>5.992730855941772</v>
       </c>
       <c r="E48" t="n">
-        <v>6.716409683227539</v>
+        <v>6.37384557723999</v>
       </c>
       <c r="F48" t="n">
-        <v>7.210732221603394</v>
+        <v>6.393741607666016</v>
       </c>
       <c r="G48" t="n">
-        <v>7.350928544998169</v>
+        <v>6.397709846496582</v>
       </c>
       <c r="H48" t="n">
-        <v>6.653068780899048</v>
+        <v>6.2640540599823</v>
       </c>
       <c r="I48" t="n">
-        <v>6.500956535339355</v>
+        <v>6.012685537338257</v>
       </c>
       <c r="J48" t="n">
-        <v>6.58225417137146</v>
+        <v>6.331886529922485</v>
       </c>
       <c r="K48" t="n">
-        <v>6.595221042633057</v>
+        <v>6.123904466629028</v>
       </c>
       <c r="L48" t="n">
-        <v>6.818029856681823</v>
+        <v>6.380137157440186</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>7.200155258178711</v>
+        <v>7.187192916870117</v>
       </c>
       <c r="C49" t="n">
-        <v>7.733324527740479</v>
+        <v>6.971299648284912</v>
       </c>
       <c r="D49" t="n">
-        <v>7.819092512130737</v>
+        <v>6.845686435699463</v>
       </c>
       <c r="E49" t="n">
-        <v>7.248552322387695</v>
+        <v>6.886979103088379</v>
       </c>
       <c r="F49" t="n">
-        <v>7.805217981338501</v>
+        <v>7.211663007736206</v>
       </c>
       <c r="G49" t="n">
-        <v>7.628196716308594</v>
+        <v>6.963751077651978</v>
       </c>
       <c r="H49" t="n">
-        <v>7.015769481658936</v>
+        <v>7.808146953582764</v>
       </c>
       <c r="I49" t="n">
-        <v>8.214706659317017</v>
+        <v>7.105464696884155</v>
       </c>
       <c r="J49" t="n">
-        <v>7.157018423080444</v>
+        <v>6.910425424575806</v>
       </c>
       <c r="K49" t="n">
-        <v>7.181378126144409</v>
+        <v>6.960294723510742</v>
       </c>
       <c r="L49" t="n">
-        <v>7.500341200828553</v>
+        <v>7.085090398788452</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>8.102463722229004</v>
+        <v>7.665494441986084</v>
       </c>
       <c r="C50" t="n">
-        <v>7.713465452194214</v>
+        <v>7.65204930305481</v>
       </c>
       <c r="D50" t="n">
-        <v>7.208285331726074</v>
+        <v>7.095585823059082</v>
       </c>
       <c r="E50" t="n">
-        <v>7.669639587402344</v>
+        <v>7.806151390075684</v>
       </c>
       <c r="F50" t="n">
-        <v>7.504383325576782</v>
+        <v>7.225578546524048</v>
       </c>
       <c r="G50" t="n">
-        <v>7.208701372146606</v>
+        <v>7.790164947509766</v>
       </c>
       <c r="H50" t="n">
-        <v>8.04255747795105</v>
+        <v>7.278991222381592</v>
       </c>
       <c r="I50" t="n">
-        <v>7.745333909988403</v>
+        <v>8.232066631317139</v>
       </c>
       <c r="J50" t="n">
-        <v>8.205156087875366</v>
+        <v>7.718838214874268</v>
       </c>
       <c r="K50" t="n">
-        <v>8.030642509460449</v>
+        <v>7.060024499893188</v>
       </c>
       <c r="L50" t="n">
-        <v>7.74306287765503</v>
+        <v>7.552494502067566</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>6.934563636779785</v>
+        <v>7.45954155921936</v>
       </c>
       <c r="C51" t="n">
-        <v>7.266518115997314</v>
+        <v>6.758291006088257</v>
       </c>
       <c r="D51" t="n">
-        <v>7.186747074127197</v>
+        <v>6.516873121261597</v>
       </c>
       <c r="E51" t="n">
-        <v>7.063511610031128</v>
+        <v>6.885999202728271</v>
       </c>
       <c r="F51" t="n">
-        <v>7.664513826370239</v>
+        <v>6.793704271316528</v>
       </c>
       <c r="G51" t="n">
-        <v>7.282955646514893</v>
+        <v>7.419114112854004</v>
       </c>
       <c r="H51" t="n">
-        <v>7.287022113800049</v>
+        <v>6.662114858627319</v>
       </c>
       <c r="I51" t="n">
-        <v>7.212142705917358</v>
+        <v>7.039062738418579</v>
       </c>
       <c r="J51" t="n">
-        <v>7.938953399658203</v>
+        <v>6.922881364822388</v>
       </c>
       <c r="K51" t="n">
-        <v>7.594832181930542</v>
+        <v>7.058512449264526</v>
       </c>
       <c r="L51" t="n">
-        <v>7.343176031112671</v>
+        <v>6.951609468460083</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8.099463329315185</v>
+        <v>7.736719198226929</v>
       </c>
       <c r="C52" t="n">
-        <v>8.113399047851562</v>
+        <v>7.617299227714539</v>
       </c>
       <c r="D52" t="n">
-        <v>8.2232661485672</v>
+        <v>7.617204375267029</v>
       </c>
       <c r="E52" t="n">
-        <v>8.173105020523071</v>
+        <v>7.524652729034424</v>
       </c>
       <c r="F52" t="n">
-        <v>8.171818885803223</v>
+        <v>7.589395437240601</v>
       </c>
       <c r="G52" t="n">
-        <v>8.288265347480774</v>
+        <v>7.566309933662414</v>
       </c>
       <c r="H52" t="n">
-        <v>7.995248212814331</v>
+        <v>7.532272505760193</v>
       </c>
       <c r="I52" t="n">
-        <v>8.022945642471313</v>
+        <v>7.58832658290863</v>
       </c>
       <c r="J52" t="n">
-        <v>8.082665925025941</v>
+        <v>7.552427730560303</v>
       </c>
       <c r="K52" t="n">
-        <v>8.107976803779602</v>
+        <v>7.62549786567688</v>
       </c>
       <c r="L52" t="n">
-        <v>8.127815436363219</v>
+        <v>7.595010558605195</v>
       </c>
     </row>
   </sheetData>
